--- a/副词.xlsx
+++ b/副词.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="338">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="342">
   <si>
     <t>非常，一点也不</t>
   </si>
@@ -438,6 +438,67 @@
   </si>
   <si>
     <t>方々</t>
+  </si>
+  <si>
+    <t>各种各样的</t>
+  </si>
+  <si>
+    <t>とかく</t>
+  </si>
+  <si>
+    <r>
+      <t>とかくの見方がある|有各种</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="128"/>
+      </rPr>
+      <t>见</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <charset val="128"/>
+      </rPr>
+      <t>解</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>とかくするうちに｜干</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="128"/>
+      </rPr>
+      <t>这</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <charset val="128"/>
+      </rPr>
+      <t>弄</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="128"/>
+      </rPr>
+      <t>啥之间</t>
+    </r>
   </si>
   <si>
     <t>已经…</t>
@@ -533,6 +594,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="128"/>
+      </rPr>
       <t>轻</t>
     </r>
     <r>
@@ -1322,7 +1389,7 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="31">
+  <fonts count="30">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1384,13 +1451,6 @@
       <color theme="1"/>
       <name val="Segoe UI Symbol"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -1846,148 +1906,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -2321,7 +2381,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F134"/>
+  <dimension ref="A1:F135"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="16.1111111111111" style="1" customWidth="1"/>
@@ -2733,10 +2793,10 @@
         <v>95</v>
       </c>
     </row>
-    <row r="49" spans="1:3">
+    <row r="49" spans="1:6">
       <c r="A49" s="6"/>
     </row>
-    <row r="50" spans="1:3">
+    <row r="50" spans="1:6">
       <c r="A50" s="6" t="s">
         <v>96</v>
       </c>
@@ -2744,7 +2804,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="51" spans="1:3">
+    <row r="51" spans="1:6">
       <c r="A51" s="6"/>
       <c r="B51" s="1" t="s">
         <v>98</v>
@@ -2753,7 +2813,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="52" spans="1:3">
+    <row r="52" spans="1:6">
       <c r="B52" s="1" t="s">
         <v>100</v>
       </c>
@@ -2761,7 +2821,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="54" spans="1:3">
+    <row r="54" spans="1:6">
       <c r="A54" s="6" t="s">
         <v>102</v>
       </c>
@@ -2772,10 +2832,10 @@
         <v>104</v>
       </c>
     </row>
-    <row r="55" spans="1:3">
+    <row r="55" spans="1:6">
       <c r="A55" s="6"/>
     </row>
-    <row r="56" spans="1:3">
+    <row r="56" spans="1:6">
       <c r="A56" s="6" t="s">
         <v>105</v>
       </c>
@@ -2786,13 +2846,13 @@
         <v>107</v>
       </c>
     </row>
-    <row r="57" spans="1:3">
+    <row r="57" spans="1:6">
       <c r="A57" s="6"/>
       <c r="B57" s="1" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="58" spans="1:3">
+    <row r="58" spans="1:6">
       <c r="A58" s="6"/>
       <c r="B58" s="1" t="s">
         <v>109</v>
@@ -2801,10 +2861,10 @@
         <v>110</v>
       </c>
     </row>
-    <row r="59" spans="1:3">
+    <row r="59" spans="1:6">
       <c r="A59" s="6"/>
     </row>
-    <row r="60" spans="1:3">
+    <row r="60" spans="1:6">
       <c r="A60" s="6" t="s">
         <v>111</v>
       </c>
@@ -2812,7 +2872,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="61" spans="1:3">
+    <row r="61" spans="1:6">
       <c r="A61" s="6" t="s">
         <v>113</v>
       </c>
@@ -2820,7 +2880,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="62" spans="1:3">
+    <row r="62" spans="1:6">
       <c r="A62" s="6" t="s">
         <v>115</v>
       </c>
@@ -2831,330 +2891,330 @@
         <v>117</v>
       </c>
     </row>
-    <row r="64" spans="1:3">
-      <c r="A64" s="6" t="s">
+    <row r="63" spans="1:6">
+      <c r="A63" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="B64" s="1" t="s">
+      <c r="B63" s="1" t="s">
         <v>119</v>
       </c>
+      <c r="E63" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>121</v>
+      </c>
     </row>
     <row r="65" spans="1:6">
+      <c r="A65" s="6" t="s">
+        <v>122</v>
+      </c>
       <c r="B65" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="C65" s="1" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6">
-      <c r="A67" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="B67" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="C67" s="1" t="s">
+    </row>
+    <row r="66" spans="1:6">
+      <c r="B66" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="D67" s="3" t="s">
+      <c r="C66" s="1" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="68" spans="1:6">
-      <c r="A68" s="6"/>
+      <c r="A68" s="6" t="s">
+        <v>126</v>
+      </c>
       <c r="B68" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="D68" s="3"/>
+        <v>127</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>129</v>
+      </c>
     </row>
     <row r="69" spans="1:6">
+      <c r="A69" s="6"/>
       <c r="B69" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="C69" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="D69"/>
-      <c r="F69"/>
+        <v>130</v>
+      </c>
+      <c r="D69" s="3"/>
     </row>
     <row r="70" spans="1:6">
       <c r="B70" s="1" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="D70"/>
+      <c r="F70"/>
     </row>
     <row r="71" spans="1:6">
       <c r="B71" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D71"/>
     </row>
     <row r="72" spans="1:6">
       <c r="B72" s="1" t="s">
-        <v>58</v>
+        <v>134</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>59</v>
+        <v>135</v>
       </c>
       <c r="D72"/>
     </row>
     <row r="73" spans="1:6">
       <c r="B73" s="1" t="s">
-        <v>132</v>
+        <v>58</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>133</v>
+        <v>59</v>
       </c>
       <c r="D73"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="A74" s="1" t="s">
-        <v>134</v>
-      </c>
       <c r="B74" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D74"/>
     </row>
     <row r="75" spans="1:6">
-      <c r="A75" s="7" t="s">
-        <v>137</v>
+      <c r="A75" s="1" t="s">
+        <v>138</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D75"/>
     </row>
     <row r="76" spans="1:6">
+      <c r="A76" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>143</v>
+      </c>
       <c r="D76"/>
     </row>
     <row r="77" spans="1:6">
-      <c r="A77" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="B77" s="1" t="s">
+      <c r="D77"/>
+    </row>
+    <row r="78" spans="1:6">
+      <c r="A78" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="B78" s="1" t="s">
         <v>34</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6">
-      <c r="B78" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="C78" s="1" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="79" spans="1:6">
       <c r="B79" s="1" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="80" spans="1:6">
-      <c r="A80" s="6" t="s">
-        <v>145</v>
-      </c>
       <c r="B80" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="D80" s="1" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="81" spans="1:4">
+      <c r="A81" s="6" t="s">
+        <v>149</v>
+      </c>
       <c r="B81" s="1" t="s">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="83" spans="1:4">
-      <c r="A83" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="B83" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="C83" s="1" t="s">
+      <c r="D81" s="1" t="s">
         <v>152</v>
       </c>
     </row>
+    <row r="82" spans="1:4">
+      <c r="B82" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
     <row r="84" spans="1:4">
+      <c r="A84" s="6" t="s">
+        <v>154</v>
+      </c>
       <c r="B84" s="1" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="85" spans="1:4">
       <c r="B85" s="1" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="D85" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="86" spans="1:4">
       <c r="B86" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>160</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="88" spans="1:4">
-      <c r="A88" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="B88" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="C88" s="1" t="s">
+    </row>
+    <row r="87" spans="1:4">
+      <c r="B87" s="1" t="s">
         <v>162</v>
       </c>
+      <c r="D87" s="1" t="s">
+        <v>163</v>
+      </c>
     </row>
     <row r="89" spans="1:4">
-      <c r="A89" s="2"/>
+      <c r="A89" s="2" t="s">
+        <v>164</v>
+      </c>
       <c r="B89" s="1" t="s">
-        <v>163</v>
+        <v>165</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="90" spans="1:4">
-      <c r="A90" s="2" t="s">
-        <v>164</v>
-      </c>
+      <c r="A90" s="2"/>
       <c r="B90" s="1" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="91" spans="1:4">
-      <c r="A91" s="5" t="s">
-        <v>166</v>
+      <c r="A91" s="2" t="s">
+        <v>168</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="92" spans="1:4">
-      <c r="A92" s="5"/>
+      <c r="A92" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>171</v>
+      </c>
     </row>
     <row r="93" spans="1:4">
-      <c r="A93" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="B93" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="C93" s="1" t="s">
-        <v>170</v>
-      </c>
+      <c r="A93" s="5"/>
     </row>
     <row r="94" spans="1:4">
-      <c r="A94" s="5"/>
+      <c r="A94" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>174</v>
+      </c>
     </row>
     <row r="95" spans="1:4">
-      <c r="A95" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="B95" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="C95" s="1" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="97" spans="1:4">
-      <c r="A97" s="6" t="s">
-        <v>174</v>
-      </c>
-      <c r="B97" s="1" t="s">
+      <c r="A95" s="5"/>
+    </row>
+    <row r="96" spans="1:4">
+      <c r="A96" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="C97" s="1" t="s">
+      <c r="B96" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="99" spans="1:4">
-      <c r="A99" s="6" t="s">
+      <c r="C96" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="B99" s="1" t="s">
+    </row>
+    <row r="98" spans="1:4">
+      <c r="A98" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="C99" s="1" t="s">
+      <c r="B98" s="1" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="101" spans="1:4">
-      <c r="A101" s="6" t="s">
+      <c r="C98" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="B101" s="1" t="s">
+    </row>
+    <row r="100" spans="1:4">
+      <c r="A100" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4">
+      <c r="A102" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="B102" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="102" spans="1:4">
-      <c r="A102" s="6"/>
-      <c r="B102" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="C102" s="6" t="s">
-        <v>182</v>
-      </c>
-      <c r="D102" s="1" t="s">
-        <v>183</v>
-      </c>
-    </row>
     <row r="103" spans="1:4">
-      <c r="A103" s="6" t="s">
-        <v>184</v>
-      </c>
+      <c r="A103" s="6"/>
       <c r="B103" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="C103" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="D103" s="1" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4">
+      <c r="A104" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="B104" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C103" s="1" t="s">
+      <c r="C104" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="104" spans="1:4">
-      <c r="A104" s="6"/>
-    </row>
     <row r="105" spans="1:4">
-      <c r="A105" s="6" t="s">
-        <v>185</v>
-      </c>
-      <c r="B105" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="C105" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="D105" s="1" t="s">
-        <v>188</v>
-      </c>
+      <c r="A105" s="6"/>
     </row>
     <row r="106" spans="1:4">
       <c r="A106" s="6" t="s">
@@ -3166,209 +3226,223 @@
       <c r="C106" s="1" t="s">
         <v>191</v>
       </c>
+      <c r="D106" s="1" t="s">
+        <v>192</v>
+      </c>
     </row>
     <row r="107" spans="1:4">
       <c r="A107" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="109" spans="1:4">
-      <c r="A109" s="6" t="s">
         <v>194</v>
       </c>
-      <c r="B109" s="1" t="s">
+      <c r="C107" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="C109" s="1" t="s">
+    </row>
+    <row r="108" spans="1:4">
+      <c r="A108" s="6" t="s">
         <v>196</v>
       </c>
+      <c r="B108" s="1" t="s">
+        <v>197</v>
+      </c>
     </row>
     <row r="110" spans="1:4">
-      <c r="A110" s="6"/>
+      <c r="A110" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>200</v>
+      </c>
     </row>
     <row r="111" spans="1:4">
-      <c r="A111" s="6" t="s">
-        <v>197</v>
-      </c>
-      <c r="B111" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="C111" s="1" t="s">
-        <v>199</v>
-      </c>
+      <c r="A111" s="6"/>
     </row>
     <row r="112" spans="1:4">
-      <c r="A112" s="6"/>
+      <c r="A112" s="6" t="s">
+        <v>201</v>
+      </c>
       <c r="B112" s="1" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="113" spans="1:3">
-      <c r="A113" s="6" t="s">
-        <v>202</v>
-      </c>
+      <c r="A113" s="6"/>
       <c r="B113" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="114" spans="1:3">
-      <c r="A114" s="6"/>
+      <c r="A114" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>208</v>
+      </c>
     </row>
     <row r="115" spans="1:3">
-      <c r="A115" s="6" t="s">
-        <v>205</v>
-      </c>
-      <c r="B115" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="C115" s="1" t="s">
-        <v>207</v>
-      </c>
+      <c r="A115" s="6"/>
     </row>
     <row r="116" spans="1:3">
       <c r="A116" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
+      </c>
+      <c r="C116" s="1" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="117" spans="1:3">
-      <c r="A117" s="1" t="s">
-        <v>210</v>
+      <c r="A117" s="6" t="s">
+        <v>212</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="118" spans="1:3">
-      <c r="A118" s="4" t="s">
-        <v>212</v>
-      </c>
-      <c r="B118" s="4" t="s">
-        <v>213</v>
-      </c>
-      <c r="C118" s="4" t="s">
+      <c r="A118" s="1" t="s">
         <v>214</v>
       </c>
+      <c r="B118" s="1" t="s">
+        <v>215</v>
+      </c>
     </row>
     <row r="119" spans="1:3">
-      <c r="A119" s="6" t="s">
-        <v>215</v>
-      </c>
-      <c r="B119" s="1" t="s">
+      <c r="A119" s="4" t="s">
         <v>216</v>
       </c>
+      <c r="B119" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="C119" s="4" t="s">
+        <v>218</v>
+      </c>
     </row>
     <row r="120" spans="1:3">
-      <c r="A120" s="4" t="s">
-        <v>217</v>
-      </c>
-      <c r="B120" s="4" t="s">
-        <v>218</v>
-      </c>
-      <c r="C120" s="4" t="s">
+      <c r="A120" s="6" t="s">
         <v>219</v>
+      </c>
+      <c r="B120" s="1" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="121" spans="1:3">
       <c r="A121" s="4" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B121" s="4" t="s">
-        <v>221</v>
+        <v>222</v>
+      </c>
+      <c r="C121" s="4" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="122" spans="1:3">
-      <c r="A122" s="6" t="s">
-        <v>222</v>
-      </c>
-      <c r="B122" s="1" t="s">
-        <v>223</v>
+      <c r="A122" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="B122" s="4" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="123" spans="1:3">
-      <c r="A123" s="8" t="s">
-        <v>224</v>
-      </c>
-      <c r="B123" s="4" t="s">
-        <v>225</v>
+      <c r="A123" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="B123" s="1" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="124" spans="1:3">
-      <c r="A124" s="6" t="s">
-        <v>226</v>
-      </c>
-      <c r="B124" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="C124" s="6" t="s">
+      <c r="A124" s="8" t="s">
         <v>228</v>
+      </c>
+      <c r="B124" s="4" t="s">
+        <v>229</v>
       </c>
     </row>
     <row r="125" spans="1:3">
       <c r="A125" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
+      </c>
+      <c r="C125" s="6" t="s">
+        <v>232</v>
       </c>
     </row>
     <row r="126" spans="1:3">
       <c r="A126" s="6" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="127" spans="1:3">
-      <c r="A127" s="9" t="s">
-        <v>233</v>
+      <c r="A127" s="6" t="s">
+        <v>235</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="C127" s="6" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="129" spans="1:2">
-      <c r="A129" s="6" t="s">
         <v>236</v>
       </c>
-      <c r="B129" s="1" t="s">
+    </row>
+    <row r="128" spans="1:3">
+      <c r="A128" s="9" t="s">
         <v>237</v>
       </c>
+      <c r="B128" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="C128" s="6" t="s">
+        <v>239</v>
+      </c>
     </row>
     <row r="130" spans="1:2">
-      <c r="A130" s="6"/>
+      <c r="A130" s="6" t="s">
+        <v>240</v>
+      </c>
       <c r="B130" s="1" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
     </row>
     <row r="131" spans="1:2">
-      <c r="A131" s="6" t="s">
-        <v>212</v>
-      </c>
+      <c r="A131" s="6"/>
       <c r="B131" s="1" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="133" spans="1:2">
-      <c r="A133" s="6"/>
+        <v>242</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2">
+      <c r="A132" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="B132" s="1" t="s">
+        <v>218</v>
+      </c>
     </row>
     <row r="134" spans="1:2">
       <c r="A134" s="6"/>
+    </row>
+    <row r="135" spans="1:2">
+      <c r="A135" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3389,67 +3463,67 @@
   <sheetData>
     <row r="1" ht="18" spans="1:3">
       <c r="A1" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
     </row>
     <row r="2" ht="18" spans="1:3">
       <c r="B2" s="1" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:3">
       <c r="B3" s="1" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:3">
       <c r="B4" s="1" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:3">
       <c r="B5" s="1" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:3">
       <c r="B6" s="1" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:3">
       <c r="A7" s="1" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:3">
       <c r="A8" s="1"/>
       <c r="B8" s="1" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="C8" s="1"/>
     </row>
@@ -3460,83 +3534,83 @@
     </row>
     <row r="10" ht="18" spans="1:3">
       <c r="A10" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
     </row>
     <row r="11" ht="18" spans="1:3">
       <c r="B11" s="1" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
     </row>
     <row r="13" ht="18" spans="1:3">
       <c r="A13" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
     </row>
     <row r="14" ht="18" spans="1:3">
       <c r="B14" s="1" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="C14" s="1"/>
     </row>
     <row r="15" ht="18" spans="1:3">
       <c r="B15" s="1" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="C15" s="1"/>
     </row>
     <row r="16" ht="18" spans="1:3">
       <c r="B16" s="1" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
     </row>
     <row r="17" ht="18" spans="1:4">
       <c r="B17" s="1" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="C17" s="1"/>
     </row>
     <row r="18" ht="18" spans="1:4">
       <c r="B18" s="1" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="C18" s="1"/>
     </row>
     <row r="19" ht="18" spans="1:4">
       <c r="B19" s="1" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="C19" s="1"/>
     </row>
     <row r="20" ht="18" spans="1:4">
       <c r="B20" s="1" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
     </row>
     <row r="21" ht="18" spans="1:4">
       <c r="B21" s="1" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
     </row>
     <row r="22" ht="18" spans="1:4">
@@ -3545,57 +3619,57 @@
     </row>
     <row r="23" ht="18" spans="1:4">
       <c r="A23" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="C23" s="1"/>
     </row>
     <row r="24" ht="18" spans="1:4">
       <c r="B24" s="1" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="C24" s="1"/>
     </row>
     <row r="25" ht="18" spans="1:4">
       <c r="B25" s="1" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
     </row>
     <row r="26" ht="18" spans="1:4">
       <c r="A26" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="D26" s="3"/>
     </row>
     <row r="27" ht="18" spans="1:4">
       <c r="A27" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="C27" s="1"/>
     </row>
     <row r="28" ht="18" spans="1:4">
       <c r="B28" s="1" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
     </row>
     <row r="29" ht="18" spans="1:4">
@@ -3604,68 +3678,68 @@
     </row>
     <row r="30" ht="18" spans="1:4">
       <c r="A30" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="C30" s="1"/>
     </row>
     <row r="31" ht="18" spans="1:4">
       <c r="B31" s="1" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="C31" s="1"/>
     </row>
     <row r="32" ht="18" spans="1:4">
       <c r="B32" s="1" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="C32" s="1"/>
     </row>
     <row r="33" ht="18" spans="1:4">
       <c r="B33" s="4" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="C33" s="1"/>
     </row>
     <row r="34" ht="18" spans="1:4">
       <c r="B34" s="4" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="C34" s="1"/>
     </row>
     <row r="35" ht="18" spans="1:4">
       <c r="B35" s="4" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
     </row>
     <row r="36" ht="18" spans="1:4">
       <c r="B36" s="4" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
     </row>
     <row r="37" ht="18" spans="1:4">
       <c r="B37" s="4" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="38" ht="18" spans="1:4">
@@ -3675,38 +3749,38 @@
     </row>
     <row r="39" ht="18" spans="1:4">
       <c r="A39" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="C39" s="1"/>
       <c r="D39" s="1"/>
     </row>
     <row r="40" ht="18" spans="1:4">
       <c r="B40" s="4" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="D40" s="1"/>
     </row>
     <row r="41" ht="18" spans="1:4">
       <c r="B41" s="4" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="D41" s="1"/>
     </row>
     <row r="42" ht="18" spans="1:4">
       <c r="B42" s="4" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="D42" s="1"/>
     </row>
@@ -3717,41 +3791,41 @@
     </row>
     <row r="44" ht="18" spans="1:4">
       <c r="A44" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="D44" s="1"/>
     </row>
     <row r="45" ht="18" spans="1:4">
       <c r="B45" s="1" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="D45" s="1"/>
     </row>
     <row r="46" ht="18" spans="1:4">
       <c r="B46" s="1" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="C46" s="4"/>
       <c r="D46" s="1"/>
     </row>
     <row r="47" ht="18" spans="1:4">
       <c r="A47" s="3" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="D47" s="1"/>
     </row>
@@ -3761,51 +3835,51 @@
     </row>
     <row r="49" ht="18" spans="1:5">
       <c r="A49" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="D49" s="5"/>
     </row>
     <row r="50" ht="18" spans="1:5">
       <c r="A50" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
     </row>
     <row r="51" ht="18" spans="1:5">
       <c r="B51" s="1" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="D51" s="1"/>
     </row>
     <row r="52" ht="18" spans="1:5">
       <c r="B52" s="1" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -3813,34 +3887,34 @@
     </row>
     <row r="54" ht="18" spans="1:5">
       <c r="A54" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
     </row>
     <row r="55" ht="18" spans="1:5">
       <c r="A55" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
     </row>
     <row r="57" ht="18" spans="1:5">
       <c r="A57" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
     </row>
     <row r="59" ht="18" spans="1:5">
       <c r="A59" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
     </row>
   </sheetData>

--- a/副词.xlsx
+++ b/副词.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="342">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="355">
   <si>
     <t>非常，一点也不</t>
   </si>
@@ -447,6 +447,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <charset val="128"/>
+      </rPr>
       <t>とかくの見方がある|有各种</t>
     </r>
     <r>
@@ -470,6 +476,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <charset val="128"/>
+      </rPr>
       <t>とかくするうちに｜干</t>
     </r>
     <r>
@@ -597,10 +609,19 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <charset val="128"/>
+      </rPr>
+      <t>一心埋</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
         <rFont val="宋体"/>
         <charset val="128"/>
       </rPr>
-      <t>轻</t>
+      <t>头</t>
     </r>
     <r>
       <rPr>
@@ -609,8 +630,13 @@
         <rFont val="Yu Gothic"/>
         <charset val="128"/>
       </rPr>
-      <t>而易</t>
-    </r>
+      <t>做...</t>
+    </r>
+  </si>
+  <si>
+    <t>せっせと</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -618,7 +644,7 @@
         <rFont val="宋体"/>
         <charset val="128"/>
       </rPr>
-      <t>举</t>
+      <t>轻</t>
     </r>
     <r>
       <rPr>
@@ -627,40 +653,17 @@
         <rFont val="Yu Gothic"/>
         <charset val="128"/>
       </rPr>
-      <t>...</t>
-    </r>
-  </si>
-  <si>
-    <t>かるがると</t>
-  </si>
-  <si>
-    <t>軽々と</t>
-  </si>
-  <si>
-    <t>一直</t>
-  </si>
-  <si>
-    <t>すぐに</t>
-  </si>
-  <si>
-    <t>直ぐに</t>
-  </si>
-  <si>
-    <t>もともと</t>
-  </si>
-  <si>
-    <t>元々</t>
-  </si>
-  <si>
-    <t>原来</t>
-  </si>
-  <si>
-    <t>やばり</t>
-  </si>
-  <si>
-    <t>矢っ張り</t>
-  </si>
-  <si>
+      <t>而易</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="128"/>
+      </rPr>
+      <t>举</t>
+    </r>
     <r>
       <rPr>
         <sz val="11"/>
@@ -668,6 +671,47 @@
         <rFont val="Yu Gothic"/>
         <charset val="128"/>
       </rPr>
+      <t>...</t>
+    </r>
+  </si>
+  <si>
+    <t>かるがると</t>
+  </si>
+  <si>
+    <t>軽々と</t>
+  </si>
+  <si>
+    <t>一直</t>
+  </si>
+  <si>
+    <t>すぐに</t>
+  </si>
+  <si>
+    <t>直ぐに</t>
+  </si>
+  <si>
+    <t>もともと</t>
+  </si>
+  <si>
+    <t>元々</t>
+  </si>
+  <si>
+    <t>原来</t>
+  </si>
+  <si>
+    <t>やばり</t>
+  </si>
+  <si>
+    <t>矢っ張り</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <charset val="128"/>
+      </rPr>
       <t>（</t>
     </r>
     <r>
@@ -772,6 +816,15 @@
     <t>だけが</t>
   </si>
   <si>
+    <t>一起</t>
+  </si>
+  <si>
+    <t>ともに</t>
+  </si>
+  <si>
+    <t>共に</t>
+  </si>
+  <si>
     <t>分别</t>
   </si>
   <si>
@@ -892,6 +945,29 @@
     <t>確かり</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="128"/>
+      </rPr>
+      <t>显</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <charset val="128"/>
+      </rPr>
+      <t>著地</t>
+    </r>
+  </si>
+  <si>
+    <t>めっきり</t>
+  </si>
+  <si>
     <t>简约地</t>
   </si>
   <si>
@@ -961,19 +1037,31 @@
     <t>たっぶり</t>
   </si>
   <si>
+    <t>☻</t>
+  </si>
+  <si>
+    <t>にっこり</t>
+  </si>
+  <si>
+    <t>smile</t>
+  </si>
+  <si>
     <t>吃惊地</t>
   </si>
   <si>
     <t>びっくり</t>
   </si>
   <si>
-    <t>☻</t>
-  </si>
-  <si>
-    <t>にっこり</t>
-  </si>
-  <si>
-    <t>smile</t>
+    <t>意外地</t>
+  </si>
+  <si>
+    <t>わりと</t>
+  </si>
+  <si>
+    <t>割とうまくいった</t>
+  </si>
+  <si>
+    <t>进展意外的顺利</t>
   </si>
   <si>
     <t>整洁地</t>
@@ -983,6 +1071,12 @@
   </si>
   <si>
     <t>ちゃんと</t>
+  </si>
+  <si>
+    <t>だまって</t>
+  </si>
+  <si>
+    <t>黙って</t>
   </si>
   <si>
     <t>但是</t>
@@ -2381,12 +2475,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F135"/>
+  <dimension ref="A1:F138"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="16.1111111111111" style="1" customWidth="1"/>
     <col min="2" max="2" width="20.4444444444444" style="1" customWidth="1"/>
-    <col min="3" max="7" width="8.88888888888889" style="1"/>
+    <col min="3" max="3" width="18.6666666666667" style="1" customWidth="1"/>
+    <col min="4" max="7" width="8.88888888888889" style="1"/>
     <col min="8" max="8" width="9.55555555555556" style="1" customWidth="1"/>
     <col min="9" max="16384" width="8.88888888888889" style="1"/>
   </cols>
@@ -3001,34 +3096,35 @@
       <c r="D75"/>
     </row>
     <row r="76" spans="1:6">
-      <c r="A76" s="7" t="s">
+      <c r="A76" s="1" t="s">
         <v>141</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="C76" s="1" t="s">
+      <c r="D76"/>
+    </row>
+    <row r="77" spans="1:6">
+      <c r="A77" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="D76"/>
-    </row>
-    <row r="77" spans="1:6">
+      <c r="B77" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>145</v>
+      </c>
       <c r="D77"/>
     </row>
     <row r="78" spans="1:6">
-      <c r="A78" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="B78" s="1" t="s">
+      <c r="D78"/>
+    </row>
+    <row r="79" spans="1:6">
+      <c r="A79" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="B79" s="1" t="s">
         <v>34</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6">
-      <c r="B79" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="C79" s="1" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="80" spans="1:6">
@@ -3040,39 +3136,39 @@
       </c>
     </row>
     <row r="81" spans="1:4">
-      <c r="A81" s="6" t="s">
+      <c r="B81" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="B81" s="1" t="s">
+      <c r="C81" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="C81" s="1" t="s">
+    </row>
+    <row r="82" spans="1:4">
+      <c r="A82" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="D81" s="1" t="s">
+      <c r="B82" s="1" t="s">
         <v>152</v>
-      </c>
-    </row>
-    <row r="82" spans="1:4">
-      <c r="B82" s="1" t="s">
-        <v>134</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="84" spans="1:4">
-      <c r="A84" s="6" t="s">
+      <c r="D82" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="B84" s="1" t="s">
+    </row>
+    <row r="83" spans="1:4">
+      <c r="B83" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="C83" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="C84" s="1" t="s">
+    </row>
+    <row r="85" spans="1:4">
+      <c r="A85" s="6" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="85" spans="1:4">
       <c r="B85" s="1" t="s">
         <v>157</v>
       </c>
@@ -3087,45 +3183,45 @@
       <c r="C86" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="D86" s="1" t="s">
-        <v>161</v>
-      </c>
     </row>
     <row r="87" spans="1:4">
       <c r="B87" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="C87" s="1" t="s">
         <v>162</v>
       </c>
       <c r="D87" s="1" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="89" spans="1:4">
-      <c r="A89" s="2" t="s">
+    <row r="88" spans="1:4">
+      <c r="B88" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="B89" s="1" t="s">
+      <c r="D88" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="C89" s="1" t="s">
+    </row>
+    <row r="90" spans="1:4">
+      <c r="A90" s="2" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="90" spans="1:4">
-      <c r="A90" s="2"/>
       <c r="B90" s="1" t="s">
         <v>167</v>
       </c>
+      <c r="C90" s="1" t="s">
+        <v>168</v>
+      </c>
     </row>
     <row r="91" spans="1:4">
-      <c r="A91" s="2" t="s">
-        <v>168</v>
-      </c>
+      <c r="A91" s="2"/>
       <c r="B91" s="1" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="92" spans="1:4">
-      <c r="A92" s="5" t="s">
+      <c r="A92" s="2" t="s">
         <v>170</v>
       </c>
       <c r="B92" s="1" t="s">
@@ -3133,155 +3229,154 @@
       </c>
     </row>
     <row r="93" spans="1:4">
-      <c r="A93" s="5"/>
+      <c r="A93" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="94" spans="1:4">
-      <c r="A94" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="B94" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="C94" s="1" t="s">
+      <c r="A94" s="5"/>
+    </row>
+    <row r="95" spans="1:4">
+      <c r="A95" s="5" t="s">
         <v>174</v>
       </c>
-    </row>
-    <row r="95" spans="1:4">
-      <c r="A95" s="5"/>
+      <c r="B95" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>176</v>
+      </c>
     </row>
     <row r="96" spans="1:4">
-      <c r="A96" s="2" t="s">
-        <v>175</v>
+      <c r="A96" s="5" t="s">
+        <v>177</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>177</v>
-      </c>
+        <v>179</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4">
+      <c r="A97" s="5"/>
     </row>
     <row r="98" spans="1:4">
-      <c r="A98" s="6" t="s">
-        <v>178</v>
+      <c r="A98" s="2" t="s">
+        <v>180</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="100" spans="1:4">
       <c r="A100" s="6" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="102" spans="1:4">
       <c r="A102" s="6" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="103" spans="1:4">
-      <c r="A103" s="6"/>
-      <c r="B103" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="C103" s="6" t="s">
-        <v>186</v>
-      </c>
-      <c r="D103" s="1" t="s">
         <v>187</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="104" spans="1:4">
       <c r="A104" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C104" s="1" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
     </row>
     <row r="105" spans="1:4">
       <c r="A105" s="6"/>
+      <c r="B105" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="C105" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="D105" s="1" t="s">
+        <v>192</v>
+      </c>
     </row>
     <row r="106" spans="1:4">
       <c r="A106" s="6" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>190</v>
+        <v>23</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="D106" s="1" t="s">
-        <v>192</v>
+        <v>24</v>
       </c>
     </row>
     <row r="107" spans="1:4">
-      <c r="A107" s="6" t="s">
-        <v>193</v>
-      </c>
-      <c r="B107" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="C107" s="1" t="s">
-        <v>195</v>
-      </c>
+      <c r="A107" s="6"/>
     </row>
     <row r="108" spans="1:4">
       <c r="A108" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="C108" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="B108" s="1" t="s">
+      <c r="D108" s="1" t="s">
         <v>197</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4">
+      <c r="A109" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="110" spans="1:4">
       <c r="A110" s="6" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="C110" s="1" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="111" spans="1:4">
-      <c r="A111" s="6"/>
+        <v>202</v>
+      </c>
     </row>
     <row r="112" spans="1:4">
       <c r="A112" s="6" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="113" spans="1:3">
       <c r="A113" s="6"/>
-      <c r="B113" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="C113" s="1" t="s">
-        <v>205</v>
-      </c>
     </row>
     <row r="114" spans="1:3">
       <c r="A114" s="6" t="s">
@@ -3296,42 +3391,43 @@
     </row>
     <row r="115" spans="1:3">
       <c r="A115" s="6"/>
+      <c r="B115" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>210</v>
+      </c>
     </row>
     <row r="116" spans="1:3">
       <c r="A116" s="6" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="117" spans="1:3">
-      <c r="A117" s="6" t="s">
-        <v>212</v>
-      </c>
-      <c r="B117" s="1" t="s">
-        <v>213</v>
-      </c>
+      <c r="A117" s="6"/>
     </row>
     <row r="118" spans="1:3">
-      <c r="A118" s="1" t="s">
+      <c r="A118" s="6" t="s">
         <v>214</v>
       </c>
       <c r="B118" s="1" t="s">
         <v>215</v>
       </c>
+      <c r="C118" s="1" t="s">
+        <v>216</v>
+      </c>
     </row>
     <row r="119" spans="1:3">
-      <c r="A119" s="4" t="s">
-        <v>216</v>
-      </c>
-      <c r="B119" s="4" t="s">
+      <c r="A119" s="7" t="s">
         <v>217</v>
       </c>
-      <c r="C119" s="4" t="s">
+      <c r="B119" s="6" t="s">
         <v>218</v>
       </c>
     </row>
@@ -3344,21 +3440,21 @@
       </c>
     </row>
     <row r="121" spans="1:3">
-      <c r="A121" s="4" t="s">
+      <c r="A121" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="B121" s="4" t="s">
+      <c r="B121" s="1" t="s">
         <v>222</v>
-      </c>
-      <c r="C121" s="4" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="122" spans="1:3">
       <c r="A122" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="B122" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="B122" s="4" t="s">
+      <c r="C122" s="4" t="s">
         <v>225</v>
       </c>
     </row>
@@ -3371,21 +3467,21 @@
       </c>
     </row>
     <row r="124" spans="1:3">
-      <c r="A124" s="8" t="s">
+      <c r="A124" s="4" t="s">
         <v>228</v>
       </c>
       <c r="B124" s="4" t="s">
         <v>229</v>
       </c>
+      <c r="C124" s="4" t="s">
+        <v>230</v>
+      </c>
     </row>
     <row r="125" spans="1:3">
-      <c r="A125" s="6" t="s">
-        <v>230</v>
-      </c>
-      <c r="B125" s="1" t="s">
+      <c r="A125" s="4" t="s">
         <v>231</v>
       </c>
-      <c r="C125" s="6" t="s">
+      <c r="B125" s="4" t="s">
         <v>232</v>
       </c>
     </row>
@@ -3398,15 +3494,15 @@
       </c>
     </row>
     <row r="127" spans="1:3">
-      <c r="A127" s="6" t="s">
+      <c r="A127" s="8" t="s">
         <v>235</v>
       </c>
-      <c r="B127" s="1" t="s">
+      <c r="B127" s="4" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="128" spans="1:3">
-      <c r="A128" s="9" t="s">
+      <c r="A128" s="6" t="s">
         <v>237</v>
       </c>
       <c r="B128" s="1" t="s">
@@ -3416,33 +3512,82 @@
         <v>239</v>
       </c>
     </row>
-    <row r="130" spans="1:2">
-      <c r="A130" s="6" t="s">
+    <row r="129" spans="1:4">
+      <c r="A129" s="6" t="s">
         <v>240</v>
       </c>
+      <c r="B129" s="1" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4">
+      <c r="A130" s="9" t="s">
+        <v>242</v>
+      </c>
       <c r="B130" s="1" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="131" spans="1:2">
-      <c r="A131" s="6"/>
+        <v>243</v>
+      </c>
+      <c r="C130" s="6" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4">
+      <c r="A131" s="6" t="s">
+        <v>245</v>
+      </c>
       <c r="B131" s="1" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="132" spans="1:2">
-      <c r="A132" s="6" t="s">
-        <v>216</v>
+        <v>246</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4">
+      <c r="A132" s="1" t="s">
+        <v>247</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="134" spans="1:2">
+        <v>248</v>
+      </c>
+      <c r="C132" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="D132" s="1" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4">
+      <c r="A133" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="B133" s="1" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4">
       <c r="A134" s="6"/>
-    </row>
-    <row r="135" spans="1:2">
-      <c r="A135" s="6"/>
+      <c r="B134" s="1" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4">
+      <c r="A135" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="B135" s="1" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4">
+      <c r="B136" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="C136" s="1" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4">
+      <c r="A137" s="6"/>
+    </row>
+    <row r="138" spans="1:4">
+      <c r="A138" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3463,67 +3608,67 @@
   <sheetData>
     <row r="1" ht="18" spans="1:3">
       <c r="A1" t="s">
-        <v>243</v>
+        <v>256</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>244</v>
+        <v>257</v>
       </c>
     </row>
     <row r="2" ht="18" spans="1:3">
       <c r="B2" s="1" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>246</v>
+        <v>259</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:3">
       <c r="B3" s="1" t="s">
-        <v>247</v>
+        <v>260</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>248</v>
+        <v>261</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:3">
       <c r="B4" s="1" t="s">
-        <v>249</v>
+        <v>262</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>250</v>
+        <v>263</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:3">
       <c r="B5" s="1" t="s">
-        <v>251</v>
+        <v>264</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>252</v>
+        <v>265</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:3">
       <c r="B6" s="1" t="s">
-        <v>253</v>
+        <v>266</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>254</v>
+        <v>267</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:3">
       <c r="A7" s="1" t="s">
-        <v>255</v>
+        <v>268</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>256</v>
+        <v>269</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>257</v>
+        <v>270</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:3">
       <c r="A8" s="1"/>
       <c r="B8" s="1" t="s">
-        <v>258</v>
+        <v>271</v>
       </c>
       <c r="C8" s="1"/>
     </row>
@@ -3534,83 +3679,83 @@
     </row>
     <row r="10" ht="18" spans="1:3">
       <c r="A10" t="s">
-        <v>259</v>
+        <v>272</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>260</v>
+        <v>273</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>261</v>
+        <v>274</v>
       </c>
     </row>
     <row r="11" ht="18" spans="1:3">
       <c r="B11" s="1" t="s">
-        <v>262</v>
+        <v>275</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>263</v>
+        <v>276</v>
       </c>
     </row>
     <row r="13" ht="18" spans="1:3">
       <c r="A13" t="s">
-        <v>264</v>
+        <v>277</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>265</v>
+        <v>278</v>
       </c>
     </row>
     <row r="14" ht="18" spans="1:3">
       <c r="B14" s="1" t="s">
-        <v>266</v>
+        <v>279</v>
       </c>
       <c r="C14" s="1"/>
     </row>
     <row r="15" ht="18" spans="1:3">
       <c r="B15" s="1" t="s">
-        <v>267</v>
+        <v>280</v>
       </c>
       <c r="C15" s="1"/>
     </row>
     <row r="16" ht="18" spans="1:3">
       <c r="B16" s="1" t="s">
-        <v>268</v>
+        <v>281</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>269</v>
+        <v>282</v>
       </c>
     </row>
     <row r="17" ht="18" spans="1:4">
       <c r="B17" s="1" t="s">
-        <v>270</v>
+        <v>283</v>
       </c>
       <c r="C17" s="1"/>
     </row>
     <row r="18" ht="18" spans="1:4">
       <c r="B18" s="1" t="s">
-        <v>271</v>
+        <v>284</v>
       </c>
       <c r="C18" s="1"/>
     </row>
     <row r="19" ht="18" spans="1:4">
       <c r="B19" s="1" t="s">
-        <v>272</v>
+        <v>285</v>
       </c>
       <c r="C19" s="1"/>
     </row>
     <row r="20" ht="18" spans="1:4">
       <c r="B20" s="1" t="s">
-        <v>273</v>
+        <v>286</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>274</v>
+        <v>287</v>
       </c>
     </row>
     <row r="21" ht="18" spans="1:4">
       <c r="B21" s="1" t="s">
-        <v>275</v>
+        <v>288</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>276</v>
+        <v>289</v>
       </c>
     </row>
     <row r="22" ht="18" spans="1:4">
@@ -3619,57 +3764,57 @@
     </row>
     <row r="23" ht="18" spans="1:4">
       <c r="A23" t="s">
-        <v>277</v>
+        <v>290</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>278</v>
+        <v>291</v>
       </c>
       <c r="C23" s="1"/>
     </row>
     <row r="24" ht="18" spans="1:4">
       <c r="B24" s="1" t="s">
-        <v>279</v>
+        <v>292</v>
       </c>
       <c r="C24" s="1"/>
     </row>
     <row r="25" ht="18" spans="1:4">
       <c r="B25" s="1" t="s">
-        <v>280</v>
+        <v>293</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>281</v>
+        <v>294</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>282</v>
+        <v>295</v>
       </c>
     </row>
     <row r="26" ht="18" spans="1:4">
       <c r="A26" t="s">
-        <v>283</v>
+        <v>296</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>284</v>
+        <v>297</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>285</v>
+        <v>298</v>
       </c>
       <c r="D26" s="3"/>
     </row>
     <row r="27" ht="18" spans="1:4">
       <c r="A27" t="s">
-        <v>286</v>
+        <v>299</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>287</v>
+        <v>300</v>
       </c>
       <c r="C27" s="1"/>
     </row>
     <row r="28" ht="18" spans="1:4">
       <c r="B28" s="1" t="s">
-        <v>288</v>
+        <v>301</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>289</v>
+        <v>302</v>
       </c>
     </row>
     <row r="29" ht="18" spans="1:4">
@@ -3678,68 +3823,68 @@
     </row>
     <row r="30" ht="18" spans="1:4">
       <c r="A30" t="s">
-        <v>290</v>
+        <v>303</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>291</v>
+        <v>304</v>
       </c>
       <c r="C30" s="1"/>
     </row>
     <row r="31" ht="18" spans="1:4">
       <c r="B31" s="1" t="s">
-        <v>292</v>
+        <v>305</v>
       </c>
       <c r="C31" s="1"/>
     </row>
     <row r="32" ht="18" spans="1:4">
       <c r="B32" s="1" t="s">
-        <v>293</v>
+        <v>306</v>
       </c>
       <c r="C32" s="1"/>
     </row>
     <row r="33" ht="18" spans="1:4">
       <c r="B33" s="4" t="s">
-        <v>294</v>
+        <v>307</v>
       </c>
       <c r="C33" s="1"/>
     </row>
     <row r="34" ht="18" spans="1:4">
       <c r="B34" s="4" t="s">
-        <v>295</v>
+        <v>308</v>
       </c>
       <c r="C34" s="1"/>
     </row>
     <row r="35" ht="18" spans="1:4">
       <c r="B35" s="4" t="s">
-        <v>296</v>
+        <v>309</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>297</v>
+        <v>310</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
     </row>
     <row r="36" ht="18" spans="1:4">
       <c r="B36" s="4" t="s">
-        <v>299</v>
+        <v>312</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>300</v>
+        <v>313</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>301</v>
+        <v>314</v>
       </c>
     </row>
     <row r="37" ht="18" spans="1:4">
       <c r="B37" s="4" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>303</v>
+        <v>316</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>304</v>
+        <v>317</v>
       </c>
     </row>
     <row r="38" ht="18" spans="1:4">
@@ -3749,38 +3894,38 @@
     </row>
     <row r="39" ht="18" spans="1:4">
       <c r="A39" t="s">
-        <v>305</v>
+        <v>318</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>306</v>
+        <v>319</v>
       </c>
       <c r="C39" s="1"/>
       <c r="D39" s="1"/>
     </row>
     <row r="40" ht="18" spans="1:4">
       <c r="B40" s="4" t="s">
-        <v>307</v>
+        <v>320</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>308</v>
+        <v>321</v>
       </c>
       <c r="D40" s="1"/>
     </row>
     <row r="41" ht="18" spans="1:4">
       <c r="B41" s="4" t="s">
-        <v>309</v>
+        <v>322</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>297</v>
+        <v>310</v>
       </c>
       <c r="D41" s="1"/>
     </row>
     <row r="42" ht="18" spans="1:4">
       <c r="B42" s="4" t="s">
-        <v>310</v>
+        <v>323</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>311</v>
+        <v>324</v>
       </c>
       <c r="D42" s="1"/>
     </row>
@@ -3791,41 +3936,41 @@
     </row>
     <row r="44" ht="18" spans="1:4">
       <c r="A44" t="s">
-        <v>312</v>
+        <v>325</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>313</v>
+        <v>326</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>314</v>
+        <v>327</v>
       </c>
       <c r="D44" s="1"/>
     </row>
     <row r="45" ht="18" spans="1:4">
       <c r="B45" s="1" t="s">
-        <v>315</v>
+        <v>328</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>316</v>
+        <v>329</v>
       </c>
       <c r="D45" s="1"/>
     </row>
     <row r="46" ht="18" spans="1:4">
       <c r="B46" s="1" t="s">
-        <v>317</v>
+        <v>330</v>
       </c>
       <c r="C46" s="4"/>
       <c r="D46" s="1"/>
     </row>
     <row r="47" ht="18" spans="1:4">
       <c r="A47" s="3" t="s">
-        <v>318</v>
+        <v>331</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>319</v>
+        <v>332</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>320</v>
+        <v>333</v>
       </c>
       <c r="D47" s="1"/>
     </row>
@@ -3835,51 +3980,51 @@
     </row>
     <row r="49" ht="18" spans="1:5">
       <c r="A49" t="s">
-        <v>321</v>
+        <v>334</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>322</v>
+        <v>335</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>323</v>
+        <v>336</v>
       </c>
       <c r="D49" s="5"/>
     </row>
     <row r="50" ht="18" spans="1:5">
       <c r="A50" t="s">
-        <v>324</v>
+        <v>337</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>325</v>
+        <v>338</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>326</v>
+        <v>339</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>327</v>
+        <v>340</v>
       </c>
     </row>
     <row r="51" ht="18" spans="1:5">
       <c r="B51" s="1" t="s">
-        <v>328</v>
+        <v>341</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>329</v>
+        <v>342</v>
       </c>
       <c r="D51" s="1"/>
     </row>
     <row r="52" ht="18" spans="1:5">
       <c r="B52" s="1" t="s">
-        <v>330</v>
+        <v>343</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>331</v>
+        <v>344</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>332</v>
+        <v>345</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>333</v>
+        <v>346</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -3887,34 +4032,34 @@
     </row>
     <row r="54" ht="18" spans="1:5">
       <c r="A54" t="s">
-        <v>334</v>
+        <v>347</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>335</v>
+        <v>348</v>
       </c>
     </row>
     <row r="55" ht="18" spans="1:5">
       <c r="A55" t="s">
-        <v>336</v>
+        <v>349</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>337</v>
+        <v>350</v>
       </c>
     </row>
     <row r="57" ht="18" spans="1:5">
       <c r="A57" t="s">
-        <v>338</v>
+        <v>351</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>339</v>
+        <v>352</v>
       </c>
     </row>
     <row r="59" ht="18" spans="1:5">
       <c r="A59" t="s">
-        <v>340</v>
+        <v>353</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>341</v>
+        <v>354</v>
       </c>
     </row>
   </sheetData>

--- a/副词.xlsx
+++ b/副词.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="355">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="363">
   <si>
     <t>非常，一点也不</t>
   </si>
@@ -87,6 +87,29 @@
   </si>
   <si>
     <t>全く</t>
+  </si>
+  <si>
+    <t>ごく</t>
+  </si>
+  <si>
+    <t>極く</t>
+  </si>
+  <si>
+    <t>ごく簡単だ</t>
+  </si>
+  <si>
+    <r>
+      <t>特别</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="128"/>
+      </rPr>
+      <t>简单</t>
+    </r>
   </si>
   <si>
     <t>とくに</t>
@@ -345,6 +368,70 @@
   </si>
   <si>
     <t>少々</t>
+  </si>
+  <si>
+    <r>
+      <t>严</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <charset val="128"/>
+      </rPr>
+      <t>重，厉害，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="128"/>
+      </rPr>
+      <t>彻</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <charset val="128"/>
+      </rPr>
+      <t>底</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>さんざんに悪罵を投げつける|狠狠</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="128"/>
+      </rPr>
+      <t>骂</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <charset val="128"/>
+      </rPr>
+      <t>一</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="128"/>
+      </rPr>
+      <t>顿</t>
+    </r>
   </si>
   <si>
     <t>确实</t>
@@ -980,103 +1067,120 @@
     <t>はっきり</t>
   </si>
   <si>
+    <t>安静地</t>
+  </si>
+  <si>
+    <t>しいんと</t>
+  </si>
+  <si>
+    <t>聚精会神地</t>
+  </si>
+  <si>
+    <t>じっと</t>
+  </si>
+  <si>
+    <t>じっと考える</t>
+  </si>
+  <si>
+    <t>心不在焉地</t>
+  </si>
+  <si>
+    <t>うっかり</t>
+  </si>
+  <si>
+    <t>严丝合缝地、合适地</t>
+  </si>
+  <si>
+    <t>ぴったり</t>
+  </si>
+  <si>
+    <t>心灰意冷地</t>
+  </si>
+  <si>
+    <t>がっかり</t>
+  </si>
+  <si>
+    <t>精疲力竭地</t>
+  </si>
+  <si>
+    <t>ぐっすり</t>
+  </si>
+  <si>
+    <t>goodsleep</t>
+  </si>
+  <si>
+    <t>充分地</t>
+  </si>
+  <si>
+    <t>たっぶり</t>
+  </si>
+  <si>
+    <t>☻</t>
+  </si>
+  <si>
+    <t>にっこり</t>
+  </si>
+  <si>
+    <t>smile</t>
+  </si>
+  <si>
+    <t>吃惊地</t>
+  </si>
+  <si>
+    <t>びっくり</t>
+  </si>
+  <si>
+    <t>意外地</t>
+  </si>
+  <si>
+    <t>わりと</t>
+  </si>
+  <si>
+    <t>割とうまくいった</t>
+  </si>
+  <si>
+    <t>进展意外的顺利</t>
+  </si>
+  <si>
+    <t>整洁地</t>
+  </si>
+  <si>
+    <t>きちんと</t>
+  </si>
+  <si>
+    <t>ちゃんと</t>
+  </si>
+  <si>
     <t>悄悄地</t>
   </si>
   <si>
+    <t>そっと</t>
+  </si>
+  <si>
+    <t>だまって</t>
+  </si>
+  <si>
+    <t>黙って</t>
+  </si>
+  <si>
     <t>こっそり</t>
   </si>
   <si>
-    <t>そっと</t>
-  </si>
-  <si>
-    <t>安静地</t>
-  </si>
-  <si>
-    <t>しいんと</t>
-  </si>
-  <si>
-    <t>聚精会神地</t>
-  </si>
-  <si>
-    <t>じっと</t>
-  </si>
-  <si>
-    <t>じっと考える</t>
-  </si>
-  <si>
-    <t>心不在焉地</t>
-  </si>
-  <si>
-    <t>うっかり</t>
-  </si>
-  <si>
-    <t>严丝合缝地、合适地</t>
-  </si>
-  <si>
-    <t>ぴったり</t>
-  </si>
-  <si>
-    <t>心灰意冷地</t>
-  </si>
-  <si>
-    <t>がっかり</t>
-  </si>
-  <si>
-    <t>精疲力竭地</t>
-  </si>
-  <si>
-    <t>ぐっすり</t>
-  </si>
-  <si>
-    <t>goodsleep</t>
-  </si>
-  <si>
-    <t>充分地</t>
-  </si>
-  <si>
-    <t>たっぶり</t>
-  </si>
-  <si>
-    <t>☻</t>
-  </si>
-  <si>
-    <t>にっこり</t>
-  </si>
-  <si>
-    <t>smile</t>
-  </si>
-  <si>
-    <t>吃惊地</t>
-  </si>
-  <si>
-    <t>びっくり</t>
-  </si>
-  <si>
-    <t>意外地</t>
-  </si>
-  <si>
-    <t>わりと</t>
-  </si>
-  <si>
-    <t>割とうまくいった</t>
-  </si>
-  <si>
-    <t>进展意外的顺利</t>
-  </si>
-  <si>
-    <t>整洁地</t>
-  </si>
-  <si>
-    <t>きちんと</t>
-  </si>
-  <si>
-    <t>ちゃんと</t>
-  </si>
-  <si>
-    <t>だまって</t>
-  </si>
-  <si>
-    <t>黙って</t>
+    <r>
+      <t>宽</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <charset val="128"/>
+      </rPr>
+      <t>敞舒适地</t>
+    </r>
+  </si>
+  <si>
+    <t>ゆったり</t>
   </si>
   <si>
     <t>但是</t>
@@ -2475,7 +2579,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F138"/>
+  <dimension ref="A1:F140"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="16.1111111111111" style="1" customWidth="1"/>
@@ -2559,705 +2663,709 @@
       </c>
     </row>
     <row r="9" spans="1:5">
+      <c r="A9" s="6"/>
       <c r="B9" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D9" s="6"/>
+      <c r="D9" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="10" spans="1:5">
       <c r="B10" s="1" t="s">
-        <v>20</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D10" s="6"/>
     </row>
     <row r="11" spans="1:5">
       <c r="B11" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="B12" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="B13" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="B14" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="B15" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D15" t="s">
-        <v>31</v>
-      </c>
-      <c r="E15" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" s="6" t="s">
+      <c r="B16" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="C16" s="1" t="s">
         <v>34</v>
       </c>
+      <c r="D16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E16" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="7" t="s">
-        <v>35</v>
+      <c r="A17" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="7"/>
-      <c r="B18" t="s">
-        <v>38</v>
+      <c r="A18" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="7"/>
       <c r="B19" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="7"/>
       <c r="B20" t="s">
-        <v>40</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="7"/>
       <c r="B21" t="s">
-        <v>42</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="7"/>
-      <c r="B22" s="1" t="s">
-        <v>44</v>
+      <c r="B22" t="s">
+        <v>46</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="7"/>
       <c r="B23" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C23" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D23" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D23" s="1" t="s">
-        <v>48</v>
+      <c r="E23" s="1" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="7"/>
-      <c r="B24"/>
+      <c r="B24" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="25" spans="1:5">
-      <c r="A25" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>51</v>
-      </c>
+      <c r="A25" s="7"/>
+      <c r="B25"/>
     </row>
     <row r="26" spans="1:5">
+      <c r="A26" s="6" t="s">
+        <v>53</v>
+      </c>
       <c r="B26" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="B27" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="B28" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="B29" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="B30" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="B31" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C31" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D31" s="1" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="33" spans="1:3">
-      <c r="A33" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="C33" s="1" t="s">
+    <row r="32" spans="1:5">
+      <c r="B32" s="1" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="34" spans="1:3">
+      <c r="C32" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4">
+      <c r="A34" s="1" t="s">
+        <v>69</v>
+      </c>
       <c r="B34" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3">
+        <v>70</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4">
       <c r="B35" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4">
       <c r="B36" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4">
       <c r="B37" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4">
       <c r="B38" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3">
-      <c r="A39" s="1" t="s">
-        <v>77</v>
-      </c>
+        <v>78</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
       <c r="B39" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4">
+      <c r="A40" s="1" t="s">
+        <v>81</v>
+      </c>
       <c r="B40" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3">
-      <c r="A42" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3">
-      <c r="A43" s="6"/>
+        <v>83</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4">
+      <c r="B41" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4">
+      <c r="A43" s="6" t="s">
+        <v>85</v>
+      </c>
       <c r="B43" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4">
+      <c r="A44" s="6"/>
       <c r="B44" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3">
-      <c r="A46" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="B46" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="C46" s="1" t="s">
+    </row>
+    <row r="45" spans="1:4">
+      <c r="B45" s="1" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="47" spans="1:3">
-      <c r="A47" s="6" t="s">
+      <c r="C45" s="1" t="s">
         <v>90</v>
       </c>
+    </row>
+    <row r="47" spans="1:4">
+      <c r="A47" s="7" t="s">
+        <v>91</v>
+      </c>
       <c r="B47" s="1" t="s">
-        <v>91</v>
+        <v>50</v>
       </c>
       <c r="C47" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D47" s="1" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="48" spans="1:3">
-      <c r="A48" s="6" t="s">
+    <row r="49" spans="1:3">
+      <c r="A49" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="B48" s="1" t="s">
+      <c r="B49" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="C48" s="1" t="s">
+      <c r="C49" s="1" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="49" spans="1:6">
-      <c r="A49" s="6"/>
-    </row>
-    <row r="50" spans="1:6">
+    <row r="50" spans="1:3">
       <c r="A50" s="6" t="s">
         <v>96</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="51" spans="1:6">
-      <c r="A51" s="6"/>
+      <c r="C50" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
+      <c r="A51" s="6" t="s">
+        <v>99</v>
+      </c>
       <c r="B51" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6">
-      <c r="B52" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="C52" s="1" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="54" spans="1:6">
-      <c r="A54" s="6" t="s">
+    <row r="52" spans="1:3">
+      <c r="A52" s="6"/>
+    </row>
+    <row r="53" spans="1:3">
+      <c r="A53" s="6" t="s">
         <v>102</v>
       </c>
+      <c r="B53" s="1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3">
+      <c r="A54" s="6"/>
       <c r="B54" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6">
-      <c r="A55" s="6"/>
-    </row>
-    <row r="56" spans="1:6">
-      <c r="A56" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="B56" s="1" t="s">
+    </row>
+    <row r="55" spans="1:3">
+      <c r="B55" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="C56" s="1" t="s">
+      <c r="C55" s="1" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="57" spans="1:6">
-      <c r="A57" s="6"/>
+    <row r="57" spans="1:3">
+      <c r="A57" s="6" t="s">
+        <v>108</v>
+      </c>
       <c r="B57" s="1" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6">
+        <v>109</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3">
       <c r="A58" s="6"/>
-      <c r="B58" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6">
-      <c r="A59" s="6"/>
-    </row>
-    <row r="60" spans="1:6">
-      <c r="A60" s="6" t="s">
+    </row>
+    <row r="59" spans="1:3">
+      <c r="A59" s="6" t="s">
         <v>111</v>
       </c>
+      <c r="B59" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3">
+      <c r="A60" s="6"/>
       <c r="B60" s="1" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6">
-      <c r="A61" s="6" t="s">
-        <v>113</v>
-      </c>
+        <v>114</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3">
+      <c r="A61" s="6"/>
       <c r="B61" s="1" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6">
-      <c r="A62" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="B62" s="1" t="s">
+      <c r="C61" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="C62" s="1" t="s">
+    </row>
+    <row r="62" spans="1:3">
+      <c r="A62" s="6"/>
+    </row>
+    <row r="63" spans="1:3">
+      <c r="A63" s="6" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="63" spans="1:6">
-      <c r="A63" s="6" t="s">
+      <c r="B63" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="B63" s="1" t="s">
+    </row>
+    <row r="64" spans="1:3">
+      <c r="A64" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="E63" s="1" t="s">
+      <c r="B64" s="1" t="s">
         <v>120</v>
-      </c>
-      <c r="F63" s="1" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="65" spans="1:6">
       <c r="A65" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="B65" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="B65" s="1" t="s">
+      <c r="C65" s="1" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="66" spans="1:6">
+      <c r="A66" s="6" t="s">
+        <v>124</v>
+      </c>
       <c r="B66" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="C66" s="1" t="s">
         <v>125</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="F66" s="1" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="68" spans="1:6">
       <c r="A68" s="6" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="C68" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="D68" s="3" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="69" spans="1:6">
-      <c r="A69" s="6"/>
       <c r="B69" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="D69" s="3"/>
-    </row>
-    <row r="70" spans="1:6">
-      <c r="B70" s="1" t="s">
+      <c r="C69" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="C70" s="1" t="s">
+    </row>
+    <row r="71" spans="1:6">
+      <c r="A71" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="D70"/>
-      <c r="F70"/>
-    </row>
-    <row r="71" spans="1:6">
       <c r="B71" s="1" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="D71"/>
+        <v>134</v>
+      </c>
+      <c r="D71" s="3" t="s">
+        <v>135</v>
+      </c>
     </row>
     <row r="72" spans="1:6">
+      <c r="A72" s="6"/>
       <c r="B72" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="C72" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="D72"/>
+        <v>136</v>
+      </c>
+      <c r="D72" s="3"/>
     </row>
     <row r="73" spans="1:6">
       <c r="B73" s="1" t="s">
-        <v>58</v>
+        <v>137</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>59</v>
+        <v>138</v>
       </c>
       <c r="D73"/>
+      <c r="F73"/>
     </row>
     <row r="74" spans="1:6">
       <c r="B74" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D74"/>
     </row>
     <row r="75" spans="1:6">
-      <c r="A75" s="1" t="s">
-        <v>138</v>
-      </c>
       <c r="B75" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D75"/>
     </row>
     <row r="76" spans="1:6">
-      <c r="A76" s="1" t="s">
-        <v>141</v>
-      </c>
       <c r="B76" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D76"/>
+    </row>
+    <row r="77" spans="1:6">
+      <c r="B77" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="D76"/>
-    </row>
-    <row r="77" spans="1:6">
-      <c r="A77" s="7" t="s">
+      <c r="C77" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="B77" s="1" t="s">
+      <c r="D77"/>
+    </row>
+    <row r="78" spans="1:6">
+      <c r="A78" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="C77" s="1" t="s">
+      <c r="B78" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="D77"/>
-    </row>
-    <row r="78" spans="1:6">
+      <c r="C78" s="1" t="s">
+        <v>146</v>
+      </c>
       <c r="D78"/>
     </row>
     <row r="79" spans="1:6">
-      <c r="A79" s="6" t="s">
-        <v>146</v>
+      <c r="A79" s="1" t="s">
+        <v>147</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>34</v>
-      </c>
+        <v>148</v>
+      </c>
+      <c r="D79"/>
     </row>
     <row r="80" spans="1:6">
+      <c r="A80" s="7" t="s">
+        <v>149</v>
+      </c>
       <c r="B80" s="1" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>148</v>
-      </c>
+        <v>151</v>
+      </c>
+      <c r="D80"/>
     </row>
     <row r="81" spans="1:4">
-      <c r="B81" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="C81" s="1" t="s">
-        <v>150</v>
-      </c>
+      <c r="D81"/>
     </row>
     <row r="82" spans="1:4">
       <c r="A82" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="C82" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="D82" s="1" t="s">
-        <v>154</v>
+        <v>38</v>
       </c>
     </row>
     <row r="83" spans="1:4">
       <c r="B83" s="1" t="s">
-        <v>134</v>
+        <v>153</v>
       </c>
       <c r="C83" s="1" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4">
+      <c r="B84" s="1" t="s">
         <v>155</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="85" spans="1:4">
       <c r="A85" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
+      </c>
+      <c r="D85" s="1" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="86" spans="1:4">
       <c r="B86" s="1" t="s">
-        <v>159</v>
+        <v>140</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="87" spans="1:4">
-      <c r="B87" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="C87" s="1" t="s">
+    </row>
+    <row r="88" spans="1:4">
+      <c r="A88" s="6" t="s">
         <v>162</v>
       </c>
-      <c r="D87" s="1" t="s">
+      <c r="B88" s="1" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="88" spans="1:4">
-      <c r="B88" s="1" t="s">
+      <c r="C88" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="D88" s="1" t="s">
+    </row>
+    <row r="89" spans="1:4">
+      <c r="B89" s="1" t="s">
         <v>165</v>
       </c>
+      <c r="C89" s="1" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="90" spans="1:4">
-      <c r="A90" s="2" t="s">
-        <v>166</v>
-      </c>
       <c r="B90" s="1" t="s">
         <v>167</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>168</v>
       </c>
+      <c r="D90" s="1" t="s">
+        <v>169</v>
+      </c>
     </row>
     <row r="91" spans="1:4">
-      <c r="A91" s="2"/>
       <c r="B91" s="1" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="92" spans="1:4">
-      <c r="A92" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="B92" s="1" t="s">
+      <c r="D91" s="1" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="93" spans="1:4">
-      <c r="A93" s="5" t="s">
+      <c r="A93" s="2" t="s">
         <v>172</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>173</v>
       </c>
+      <c r="C93" s="1" t="s">
+        <v>174</v>
+      </c>
     </row>
     <row r="94" spans="1:4">
-      <c r="A94" s="5"/>
+      <c r="A94" s="2"/>
+      <c r="B94" s="1" t="s">
+        <v>175</v>
+      </c>
     </row>
     <row r="95" spans="1:4">
-      <c r="A95" s="5" t="s">
-        <v>174</v>
+      <c r="A95" s="2" t="s">
+        <v>176</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="C95" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="96" spans="1:4">
       <c r="A96" s="5" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="C96" s="1" t="s">
         <v>179</v>
       </c>
     </row>
@@ -3265,7 +3373,7 @@
       <c r="A97" s="5"/>
     </row>
     <row r="98" spans="1:4">
-      <c r="A98" s="2" t="s">
+      <c r="A98" s="5" t="s">
         <v>180</v>
       </c>
       <c r="B98" s="1" t="s">
@@ -3275,147 +3383,147 @@
         <v>182</v>
       </c>
     </row>
+    <row r="99" spans="1:4">
+      <c r="A99" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>185</v>
+      </c>
+    </row>
     <row r="100" spans="1:4">
-      <c r="A100" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="B100" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="C100" s="1" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="102" spans="1:4">
-      <c r="A102" s="6" t="s">
+      <c r="A100" s="5"/>
+    </row>
+    <row r="101" spans="1:4">
+      <c r="A101" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="B102" s="1" t="s">
+      <c r="B101" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="C102" s="1" t="s">
+      <c r="C101" s="1" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="104" spans="1:4">
-      <c r="A104" s="6" t="s">
+    <row r="103" spans="1:4">
+      <c r="A103" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="B104" s="1" t="s">
+      <c r="B103" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4">
+      <c r="A105" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4">
+      <c r="A107" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="B107" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="105" spans="1:4">
-      <c r="A105" s="6"/>
-      <c r="B105" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="C105" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="D105" s="1" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="106" spans="1:4">
-      <c r="A106" s="6" t="s">
-        <v>193</v>
-      </c>
-      <c r="B106" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C106" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="107" spans="1:4">
-      <c r="A107" s="6"/>
-    </row>
     <row r="108" spans="1:4">
-      <c r="A108" s="6" t="s">
-        <v>194</v>
-      </c>
+      <c r="A108" s="6"/>
       <c r="B108" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="C108" s="1" t="s">
         <v>196</v>
       </c>
+      <c r="C108" s="6" t="s">
+        <v>197</v>
+      </c>
       <c r="D108" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="109" spans="1:4">
       <c r="A109" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>199</v>
+        <v>27</v>
       </c>
       <c r="C109" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4">
+      <c r="A110" s="6"/>
+    </row>
+    <row r="111" spans="1:4">
+      <c r="A111" s="6" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="110" spans="1:4">
-      <c r="A110" s="6" t="s">
+      <c r="B111" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="B110" s="1" t="s">
+      <c r="C111" s="1" t="s">
         <v>202</v>
+      </c>
+      <c r="D111" s="1" t="s">
+        <v>203</v>
       </c>
     </row>
     <row r="112" spans="1:4">
       <c r="A112" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="113" spans="1:3">
-      <c r="A113" s="6"/>
-    </row>
-    <row r="114" spans="1:3">
-      <c r="A114" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="B114" s="1" t="s">
+      <c r="A113" s="6" t="s">
         <v>207</v>
       </c>
-      <c r="C114" s="1" t="s">
+      <c r="B113" s="1" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="115" spans="1:3">
-      <c r="A115" s="6"/>
+      <c r="A115" s="6" t="s">
+        <v>209</v>
+      </c>
       <c r="B115" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="116" spans="1:3">
-      <c r="A116" s="6" t="s">
-        <v>211</v>
-      </c>
-      <c r="B116" s="1" t="s">
+      <c r="A116" s="6"/>
+    </row>
+    <row r="117" spans="1:3">
+      <c r="A117" s="6" t="s">
         <v>212</v>
       </c>
-      <c r="C116" s="1" t="s">
+      <c r="B117" s="1" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="117" spans="1:3">
-      <c r="A117" s="6"/>
+      <c r="C117" s="1" t="s">
+        <v>214</v>
+      </c>
     </row>
     <row r="118" spans="1:3">
-      <c r="A118" s="6" t="s">
-        <v>214</v>
-      </c>
+      <c r="A118" s="6"/>
       <c r="B118" s="1" t="s">
         <v>215</v>
       </c>
@@ -3424,170 +3532,195 @@
       </c>
     </row>
     <row r="119" spans="1:3">
-      <c r="A119" s="7" t="s">
+      <c r="A119" s="6" t="s">
         <v>217</v>
       </c>
-      <c r="B119" s="6" t="s">
+      <c r="B119" s="1" t="s">
         <v>218</v>
       </c>
+      <c r="C119" s="1" t="s">
+        <v>219</v>
+      </c>
     </row>
     <row r="120" spans="1:3">
-      <c r="A120" s="6" t="s">
-        <v>219</v>
-      </c>
-      <c r="B120" s="1" t="s">
+      <c r="A120" s="6"/>
+    </row>
+    <row r="121" spans="1:3">
+      <c r="A121" s="6" t="s">
         <v>220</v>
       </c>
-    </row>
-    <row r="121" spans="1:3">
-      <c r="A121" s="1" t="s">
+      <c r="B121" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="B121" s="1" t="s">
+      <c r="C121" s="1" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="122" spans="1:3">
-      <c r="A122" s="4" t="s">
+      <c r="A122" s="7" t="s">
         <v>223</v>
       </c>
-      <c r="B122" s="4" t="s">
+      <c r="B122" s="6" t="s">
         <v>224</v>
-      </c>
-      <c r="C122" s="4" t="s">
-        <v>225</v>
       </c>
     </row>
     <row r="123" spans="1:3">
       <c r="A123" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="B123" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="B123" s="1" t="s">
+    </row>
+    <row r="124" spans="1:3">
+      <c r="A124" s="1" t="s">
         <v>227</v>
       </c>
-    </row>
-    <row r="124" spans="1:3">
-      <c r="A124" s="4" t="s">
+      <c r="B124" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="B124" s="4" t="s">
+    </row>
+    <row r="125" spans="1:3">
+      <c r="A125" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="C124" s="4" t="s">
+      <c r="B125" s="1" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="125" spans="1:3">
-      <c r="A125" s="4" t="s">
+    <row r="126" spans="1:3">
+      <c r="A126" s="4" t="s">
         <v>231</v>
       </c>
-      <c r="B125" s="4" t="s">
+      <c r="B126" s="4" t="s">
         <v>232</v>
       </c>
-    </row>
-    <row r="126" spans="1:3">
-      <c r="A126" s="6" t="s">
+      <c r="C126" s="4" t="s">
         <v>233</v>
       </c>
-      <c r="B126" s="1" t="s">
+    </row>
+    <row r="127" spans="1:3">
+      <c r="A127" s="4" t="s">
         <v>234</v>
       </c>
-    </row>
-    <row r="127" spans="1:3">
-      <c r="A127" s="8" t="s">
+      <c r="B127" s="4" t="s">
         <v>235</v>
-      </c>
-      <c r="B127" s="4" t="s">
-        <v>236</v>
       </c>
     </row>
     <row r="128" spans="1:3">
       <c r="A128" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="B128" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="B128" s="1" t="s">
+    </row>
+    <row r="129" spans="1:4">
+      <c r="A129" s="8" t="s">
         <v>238</v>
       </c>
-      <c r="C128" s="6" t="s">
+      <c r="B129" s="4" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="129" spans="1:4">
-      <c r="A129" s="6" t="s">
+    <row r="130" spans="1:4">
+      <c r="A130" s="6" t="s">
         <v>240</v>
       </c>
-      <c r="B129" s="1" t="s">
+      <c r="B130" s="1" t="s">
         <v>241</v>
       </c>
-    </row>
-    <row r="130" spans="1:4">
-      <c r="A130" s="9" t="s">
+      <c r="C130" s="6" t="s">
         <v>242</v>
-      </c>
-      <c r="B130" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="C130" s="6" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="131" spans="1:4">
       <c r="A131" s="6" t="s">
+        <v>243</v>
+      </c>
+      <c r="B131" s="1" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4">
+      <c r="A132" s="9" t="s">
         <v>245</v>
       </c>
-      <c r="B131" s="1" t="s">
+      <c r="B132" s="1" t="s">
         <v>246</v>
       </c>
-    </row>
-    <row r="132" spans="1:4">
-      <c r="A132" s="1" t="s">
+      <c r="C132" s="6" t="s">
         <v>247</v>
-      </c>
-      <c r="B132" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="C132" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="D132" s="1" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="133" spans="1:4">
       <c r="A133" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="B133" s="1" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4">
+      <c r="A134" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="B134" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="B133" s="1" t="s">
+      <c r="C134" s="1" t="s">
         <v>252</v>
       </c>
-    </row>
-    <row r="134" spans="1:4">
-      <c r="A134" s="6"/>
-      <c r="B134" s="1" t="s">
+      <c r="D134" s="1" t="s">
         <v>253</v>
       </c>
     </row>
     <row r="135" spans="1:4">
       <c r="A135" s="6" t="s">
-        <v>223</v>
+        <v>254</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>225</v>
+        <v>255</v>
       </c>
     </row>
     <row r="136" spans="1:4">
+      <c r="A136" s="6"/>
       <c r="B136" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="C136" s="1" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="137" spans="1:4">
-      <c r="A137" s="6"/>
+      <c r="A137" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="B137" s="1" t="s">
+        <v>258</v>
+      </c>
     </row>
     <row r="138" spans="1:4">
-      <c r="A138" s="6"/>
+      <c r="B138" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="C138" s="1" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4">
+      <c r="A139" s="6"/>
+      <c r="B139" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="C139" s="4" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4">
+      <c r="A140" s="7" t="s">
+        <v>262</v>
+      </c>
+      <c r="B140" s="6" t="s">
+        <v>263</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3608,67 +3741,67 @@
   <sheetData>
     <row r="1" ht="18" spans="1:3">
       <c r="A1" t="s">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>257</v>
+        <v>265</v>
       </c>
     </row>
     <row r="2" ht="18" spans="1:3">
       <c r="B2" s="1" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:3">
       <c r="B3" s="1" t="s">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:3">
       <c r="B4" s="1" t="s">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:3">
       <c r="B5" s="1" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:3">
       <c r="B6" s="1" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:3">
       <c r="A7" s="1" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:3">
       <c r="A8" s="1"/>
       <c r="B8" s="1" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="C8" s="1"/>
     </row>
@@ -3679,83 +3812,83 @@
     </row>
     <row r="10" ht="18" spans="1:3">
       <c r="A10" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>274</v>
+        <v>282</v>
       </c>
     </row>
     <row r="11" ht="18" spans="1:3">
       <c r="B11" s="1" t="s">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>276</v>
+        <v>284</v>
       </c>
     </row>
     <row r="13" ht="18" spans="1:3">
       <c r="A13" t="s">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
     </row>
     <row r="14" ht="18" spans="1:3">
       <c r="B14" s="1" t="s">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="C14" s="1"/>
     </row>
     <row r="15" ht="18" spans="1:3">
       <c r="B15" s="1" t="s">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="C15" s="1"/>
     </row>
     <row r="16" ht="18" spans="1:3">
       <c r="B16" s="1" t="s">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>282</v>
+        <v>290</v>
       </c>
     </row>
     <row r="17" ht="18" spans="1:4">
       <c r="B17" s="1" t="s">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="C17" s="1"/>
     </row>
     <row r="18" ht="18" spans="1:4">
       <c r="B18" s="1" t="s">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="C18" s="1"/>
     </row>
     <row r="19" ht="18" spans="1:4">
       <c r="B19" s="1" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="C19" s="1"/>
     </row>
     <row r="20" ht="18" spans="1:4">
       <c r="B20" s="1" t="s">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>287</v>
+        <v>295</v>
       </c>
     </row>
     <row r="21" ht="18" spans="1:4">
       <c r="B21" s="1" t="s">
-        <v>288</v>
+        <v>296</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>289</v>
+        <v>297</v>
       </c>
     </row>
     <row r="22" ht="18" spans="1:4">
@@ -3764,57 +3897,57 @@
     </row>
     <row r="23" ht="18" spans="1:4">
       <c r="A23" t="s">
-        <v>290</v>
+        <v>298</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>291</v>
+        <v>299</v>
       </c>
       <c r="C23" s="1"/>
     </row>
     <row r="24" ht="18" spans="1:4">
       <c r="B24" s="1" t="s">
-        <v>292</v>
+        <v>300</v>
       </c>
       <c r="C24" s="1"/>
     </row>
     <row r="25" ht="18" spans="1:4">
       <c r="B25" s="1" t="s">
-        <v>293</v>
+        <v>301</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>294</v>
+        <v>302</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>295</v>
+        <v>303</v>
       </c>
     </row>
     <row r="26" ht="18" spans="1:4">
       <c r="A26" t="s">
-        <v>296</v>
+        <v>304</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>297</v>
+        <v>305</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="D26" s="3"/>
     </row>
     <row r="27" ht="18" spans="1:4">
       <c r="A27" t="s">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="C27" s="1"/>
     </row>
     <row r="28" ht="18" spans="1:4">
       <c r="B28" s="1" t="s">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
     </row>
     <row r="29" ht="18" spans="1:4">
@@ -3823,68 +3956,68 @@
     </row>
     <row r="30" ht="18" spans="1:4">
       <c r="A30" t="s">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="C30" s="1"/>
     </row>
     <row r="31" ht="18" spans="1:4">
       <c r="B31" s="1" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="C31" s="1"/>
     </row>
     <row r="32" ht="18" spans="1:4">
       <c r="B32" s="1" t="s">
-        <v>306</v>
+        <v>314</v>
       </c>
       <c r="C32" s="1"/>
     </row>
     <row r="33" ht="18" spans="1:4">
       <c r="B33" s="4" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
       <c r="C33" s="1"/>
     </row>
     <row r="34" ht="18" spans="1:4">
       <c r="B34" s="4" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="C34" s="1"/>
     </row>
     <row r="35" ht="18" spans="1:4">
       <c r="B35" s="4" t="s">
-        <v>309</v>
+        <v>317</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>310</v>
+        <v>318</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
     </row>
     <row r="36" ht="18" spans="1:4">
       <c r="B36" s="4" t="s">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>314</v>
+        <v>322</v>
       </c>
     </row>
     <row r="37" ht="18" spans="1:4">
       <c r="B37" s="4" t="s">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>317</v>
+        <v>325</v>
       </c>
     </row>
     <row r="38" ht="18" spans="1:4">
@@ -3894,38 +4027,38 @@
     </row>
     <row r="39" ht="18" spans="1:4">
       <c r="A39" t="s">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="C39" s="1"/>
       <c r="D39" s="1"/>
     </row>
     <row r="40" ht="18" spans="1:4">
       <c r="B40" s="4" t="s">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>321</v>
+        <v>329</v>
       </c>
       <c r="D40" s="1"/>
     </row>
     <row r="41" ht="18" spans="1:4">
       <c r="B41" s="4" t="s">
-        <v>322</v>
+        <v>330</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>310</v>
+        <v>318</v>
       </c>
       <c r="D41" s="1"/>
     </row>
     <row r="42" ht="18" spans="1:4">
       <c r="B42" s="4" t="s">
-        <v>323</v>
+        <v>331</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="D42" s="1"/>
     </row>
@@ -3936,41 +4069,41 @@
     </row>
     <row r="44" ht="18" spans="1:4">
       <c r="A44" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="D44" s="1"/>
     </row>
     <row r="45" ht="18" spans="1:4">
       <c r="B45" s="1" t="s">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>329</v>
+        <v>337</v>
       </c>
       <c r="D45" s="1"/>
     </row>
     <row r="46" ht="18" spans="1:4">
       <c r="B46" s="1" t="s">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="C46" s="4"/>
       <c r="D46" s="1"/>
     </row>
     <row r="47" ht="18" spans="1:4">
       <c r="A47" s="3" t="s">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="D47" s="1"/>
     </row>
@@ -3980,51 +4113,51 @@
     </row>
     <row r="49" ht="18" spans="1:5">
       <c r="A49" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c r="D49" s="5"/>
     </row>
     <row r="50" ht="18" spans="1:5">
       <c r="A50" t="s">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>340</v>
+        <v>348</v>
       </c>
     </row>
     <row r="51" ht="18" spans="1:5">
       <c r="B51" s="1" t="s">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>342</v>
+        <v>350</v>
       </c>
       <c r="D51" s="1"/>
     </row>
     <row r="52" ht="18" spans="1:5">
       <c r="B52" s="1" t="s">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>344</v>
+        <v>352</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>345</v>
+        <v>353</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>346</v>
+        <v>354</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -4032,34 +4165,34 @@
     </row>
     <row r="54" ht="18" spans="1:5">
       <c r="A54" t="s">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>348</v>
+        <v>356</v>
       </c>
     </row>
     <row r="55" ht="18" spans="1:5">
       <c r="A55" t="s">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>350</v>
+        <v>358</v>
       </c>
     </row>
     <row r="57" ht="18" spans="1:5">
       <c r="A57" t="s">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>352</v>
+        <v>360</v>
       </c>
     </row>
     <row r="59" ht="18" spans="1:5">
       <c r="A59" t="s">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>354</v>
+        <v>362</v>
       </c>
     </row>
   </sheetData>

--- a/副词.xlsx
+++ b/副词.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9180"/>
+    <workbookView windowWidth="22188" windowHeight="9180"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="363">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="368">
   <si>
     <t>非常，一点也不</t>
   </si>
@@ -99,6 +99,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <charset val="128"/>
+      </rPr>
       <t>特别</t>
     </r>
     <r>
@@ -239,13 +245,16 @@
     </r>
   </si>
   <si>
+    <t>もっとも</t>
+  </si>
+  <si>
+    <t>最も</t>
+  </si>
+  <si>
+    <t>（最...）</t>
+  </si>
+  <si>
     <t>更加…</t>
-  </si>
-  <si>
-    <t>もっと</t>
-  </si>
-  <si>
-    <t>最も</t>
   </si>
   <si>
     <t>さらに</t>
@@ -371,6 +380,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="128"/>
+      </rPr>
       <t>严</t>
     </r>
     <r>
@@ -403,6 +418,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <charset val="128"/>
+      </rPr>
       <t>さんざんに悪罵を投げつける|狠狠</t>
     </r>
     <r>
@@ -912,6 +933,12 @@
     <t>共に</t>
   </si>
   <si>
+    <t>いっせいに</t>
+  </si>
+  <si>
+    <t>一斉に</t>
+  </si>
+  <si>
     <t>分别</t>
   </si>
   <si>
@@ -1142,6 +1169,12 @@
     <t>进展意外的顺利</t>
   </si>
   <si>
+    <t>恍惚地</t>
+  </si>
+  <si>
+    <t>ぼうっと</t>
+  </si>
+  <si>
     <t>整洁地</t>
   </si>
   <si>
@@ -1167,6 +1200,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="128"/>
+      </rPr>
       <t>宽</t>
     </r>
     <r>
@@ -2579,7 +2618,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F140"/>
+  <dimension ref="A1:F142"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="16.1111111111111" style="1" customWidth="1"/>
@@ -2812,171 +2851,175 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="7"/>
-      <c r="B25"/>
+      <c r="B25" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="26" spans="1:5">
-      <c r="A26" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>55</v>
-      </c>
+      <c r="A26" s="7"/>
+      <c r="B26"/>
     </row>
     <row r="27" spans="1:5">
+      <c r="A27" s="6" t="s">
+        <v>56</v>
+      </c>
       <c r="B27" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="B28" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="B29" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="B30" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="B31" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D31" s="1" t="s">
         <v>65</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="B32" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="B35" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="36" spans="1:4">
       <c r="B36" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="37" spans="1:4">
       <c r="B37" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="38" spans="1:4">
       <c r="B38" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="39" spans="1:4">
       <c r="B39" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="41" spans="1:4">
       <c r="B41" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="43" spans="1:4">
       <c r="A43" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="44" spans="1:4">
       <c r="A44" s="6"/>
       <c r="B44" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="45" spans="1:4">
       <c r="B45" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>50</v>
@@ -2985,40 +3028,40 @@
         <v>51</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -3026,38 +3069,38 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54" s="6"/>
       <c r="B54" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="B55" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -3065,28 +3108,28 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60" s="6"/>
       <c r="B60" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61" s="6"/>
       <c r="B61" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -3094,158 +3137,158 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="65" spans="1:6">
       <c r="A65" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="66" spans="1:6">
       <c r="A66" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="68" spans="1:6">
       <c r="A68" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="69" spans="1:6">
       <c r="B69" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="71" spans="1:6">
       <c r="A71" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="72" spans="1:6">
       <c r="A72" s="6"/>
       <c r="B72" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D72" s="3"/>
     </row>
     <row r="73" spans="1:6">
       <c r="B73" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D73"/>
       <c r="F73"/>
     </row>
     <row r="74" spans="1:6">
       <c r="B74" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D74"/>
     </row>
     <row r="75" spans="1:6">
       <c r="B75" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D75"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D76"/>
     </row>
     <row r="77" spans="1:6">
       <c r="B77" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D77"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D78"/>
     </row>
     <row r="79" spans="1:6">
       <c r="A79" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D79"/>
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="7" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D80"/>
     </row>
@@ -3254,7 +3297,7 @@
     </row>
     <row r="82" spans="1:4">
       <c r="A82" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>38</v>
@@ -3262,111 +3305,111 @@
     </row>
     <row r="83" spans="1:4">
       <c r="B83" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="84" spans="1:4">
       <c r="B84" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="85" spans="1:4">
       <c r="A85" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="86" spans="1:4">
       <c r="B86" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="88" spans="1:4">
       <c r="A88" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="89" spans="1:4">
       <c r="B89" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="90" spans="1:4">
       <c r="B90" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="91" spans="1:4">
       <c r="B91" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="93" spans="1:4">
       <c r="A93" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="94" spans="1:4">
       <c r="A94" s="2"/>
       <c r="B94" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="95" spans="1:4">
       <c r="A95" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="96" spans="1:4">
       <c r="A96" s="5" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3374,19 +3417,17 @@
     </row>
     <row r="98" spans="1:4">
       <c r="A98" s="5" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="99" spans="1:4">
-      <c r="A99" s="5" t="s">
-        <v>183</v>
-      </c>
+      <c r="A99" s="5"/>
       <c r="B99" s="1" t="s">
         <v>184</v>
       </c>
@@ -3395,97 +3436,97 @@
       </c>
     </row>
     <row r="100" spans="1:4">
-      <c r="A100" s="5"/>
+      <c r="A100" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>188</v>
+      </c>
     </row>
     <row r="101" spans="1:4">
-      <c r="A101" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="B101" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="C101" s="1" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="103" spans="1:4">
-      <c r="A103" s="6" t="s">
+      <c r="A101" s="5"/>
+    </row>
+    <row r="102" spans="1:4">
+      <c r="A102" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="B103" s="1" t="s">
+      <c r="B102" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="C103" s="1" t="s">
+      <c r="C102" s="1" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="105" spans="1:4">
-      <c r="A105" s="6" t="s">
+    <row r="104" spans="1:4">
+      <c r="A104" s="6" t="s">
         <v>192</v>
       </c>
-      <c r="B105" s="1" t="s">
+      <c r="B104" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="C105" s="1" t="s">
+      <c r="C104" s="1" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="107" spans="1:4">
-      <c r="A107" s="6" t="s">
+    <row r="106" spans="1:4">
+      <c r="A106" s="6" t="s">
         <v>195</v>
       </c>
-      <c r="B107" s="1" t="s">
+      <c r="B106" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4">
+      <c r="A108" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="B108" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="108" spans="1:4">
-      <c r="A108" s="6"/>
-      <c r="B108" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="C108" s="6" t="s">
-        <v>197</v>
-      </c>
-      <c r="D108" s="1" t="s">
-        <v>198</v>
-      </c>
-    </row>
     <row r="109" spans="1:4">
-      <c r="A109" s="6" t="s">
+      <c r="A109" s="6"/>
+      <c r="B109" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="B109" s="1" t="s">
+      <c r="C109" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="D109" s="1" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4">
+      <c r="A110" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="B110" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C109" s="1" t="s">
+      <c r="C110" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="110" spans="1:4">
-      <c r="A110" s="6"/>
-    </row>
     <row r="111" spans="1:4">
-      <c r="A111" s="6" t="s">
-        <v>200</v>
-      </c>
-      <c r="B111" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="C111" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="D111" s="1" t="s">
-        <v>203</v>
-      </c>
+      <c r="A111" s="6"/>
     </row>
     <row r="112" spans="1:4">
       <c r="A112" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="B112" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="B112" s="1" t="s">
+      <c r="C112" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="C112" s="1" t="s">
+      <c r="D112" s="1" t="s">
         <v>206</v>
       </c>
     </row>
@@ -3496,45 +3537,45 @@
       <c r="B113" s="1" t="s">
         <v>208</v>
       </c>
-    </row>
-    <row r="115" spans="1:3">
-      <c r="A115" s="6" t="s">
+      <c r="C113" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="B115" s="1" t="s">
+    </row>
+    <row r="114" spans="1:3">
+      <c r="A114" s="6" t="s">
         <v>210</v>
       </c>
-      <c r="C115" s="1" t="s">
+      <c r="B114" s="1" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="116" spans="1:3">
-      <c r="A116" s="6"/>
+      <c r="A116" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="B116" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="C116" s="1" t="s">
+        <v>214</v>
+      </c>
     </row>
     <row r="117" spans="1:3">
-      <c r="A117" s="6" t="s">
-        <v>212</v>
-      </c>
-      <c r="B117" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="C117" s="1" t="s">
-        <v>214</v>
-      </c>
+      <c r="A117" s="6"/>
     </row>
     <row r="118" spans="1:3">
-      <c r="A118" s="6"/>
+      <c r="A118" s="6" t="s">
+        <v>215</v>
+      </c>
       <c r="B118" s="1" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="119" spans="1:3">
-      <c r="A119" s="6" t="s">
-        <v>217</v>
-      </c>
+      <c r="A119" s="6"/>
       <c r="B119" s="1" t="s">
         <v>218</v>
       </c>
@@ -3543,59 +3584,59 @@
       </c>
     </row>
     <row r="120" spans="1:3">
-      <c r="A120" s="6"/>
+      <c r="A120" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="B120" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="C120" s="1" t="s">
+        <v>222</v>
+      </c>
     </row>
     <row r="121" spans="1:3">
-      <c r="A121" s="6" t="s">
-        <v>220</v>
-      </c>
-      <c r="B121" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="C121" s="1" t="s">
-        <v>222</v>
-      </c>
+      <c r="A121" s="6"/>
     </row>
     <row r="122" spans="1:3">
-      <c r="A122" s="7" t="s">
+      <c r="A122" s="6" t="s">
         <v>223</v>
       </c>
-      <c r="B122" s="6" t="s">
+      <c r="B122" s="1" t="s">
         <v>224</v>
       </c>
+      <c r="C122" s="1" t="s">
+        <v>225</v>
+      </c>
     </row>
     <row r="123" spans="1:3">
-      <c r="A123" s="6" t="s">
-        <v>225</v>
-      </c>
-      <c r="B123" s="1" t="s">
+      <c r="A123" s="7" t="s">
         <v>226</v>
       </c>
+      <c r="B123" s="6" t="s">
+        <v>227</v>
+      </c>
     </row>
     <row r="124" spans="1:3">
-      <c r="A124" s="1" t="s">
-        <v>227</v>
+      <c r="A124" s="6" t="s">
+        <v>228</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="125" spans="1:3">
-      <c r="A125" s="6" t="s">
-        <v>229</v>
+      <c r="A125" s="1" t="s">
+        <v>230</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="126" spans="1:3">
-      <c r="A126" s="4" t="s">
-        <v>231</v>
-      </c>
-      <c r="B126" s="4" t="s">
+      <c r="A126" s="6" t="s">
         <v>232</v>
       </c>
-      <c r="C126" s="4" t="s">
+      <c r="B126" s="1" t="s">
         <v>233</v>
       </c>
     </row>
@@ -3606,31 +3647,31 @@
       <c r="B127" s="4" t="s">
         <v>235</v>
       </c>
+      <c r="C127" s="4" t="s">
+        <v>236</v>
+      </c>
     </row>
     <row r="128" spans="1:3">
-      <c r="A128" s="6" t="s">
-        <v>236</v>
-      </c>
-      <c r="B128" s="1" t="s">
+      <c r="A128" s="4" t="s">
         <v>237</v>
       </c>
+      <c r="B128" s="4" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="129" spans="1:4">
-      <c r="A129" s="8" t="s">
-        <v>238</v>
-      </c>
-      <c r="B129" s="4" t="s">
+      <c r="A129" s="6" t="s">
         <v>239</v>
       </c>
+      <c r="B129" s="1" t="s">
+        <v>240</v>
+      </c>
     </row>
     <row r="130" spans="1:4">
-      <c r="A130" s="6" t="s">
-        <v>240</v>
-      </c>
-      <c r="B130" s="1" t="s">
+      <c r="A130" s="8" t="s">
         <v>241</v>
       </c>
-      <c r="C130" s="6" t="s">
+      <c r="B130" s="4" t="s">
         <v>242</v>
       </c>
     </row>
@@ -3641,85 +3682,104 @@
       <c r="B131" s="1" t="s">
         <v>244</v>
       </c>
+      <c r="C131" s="6" t="s">
+        <v>245</v>
+      </c>
     </row>
     <row r="132" spans="1:4">
-      <c r="A132" s="9" t="s">
-        <v>245</v>
+      <c r="A132" s="6" t="s">
+        <v>246</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="C132" s="6" t="s">
         <v>247</v>
       </c>
     </row>
     <row r="133" spans="1:4">
-      <c r="A133" s="6" t="s">
+      <c r="A133" s="9" t="s">
         <v>248</v>
       </c>
       <c r="B133" s="1" t="s">
         <v>249</v>
       </c>
+      <c r="C133" s="6" t="s">
+        <v>250</v>
+      </c>
     </row>
     <row r="134" spans="1:4">
-      <c r="A134" s="1" t="s">
-        <v>250</v>
+      <c r="A134" s="6" t="s">
+        <v>251</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="C134" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="D134" s="1" t="s">
+    </row>
+    <row r="135" spans="1:4">
+      <c r="A135" s="1" t="s">
         <v>253</v>
       </c>
-    </row>
-    <row r="135" spans="1:4">
-      <c r="A135" s="6" t="s">
+      <c r="B135" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="B135" s="1" t="s">
+      <c r="C135" s="1" t="s">
         <v>255</v>
       </c>
+      <c r="D135" s="1" t="s">
+        <v>256</v>
+      </c>
     </row>
     <row r="136" spans="1:4">
-      <c r="A136" s="6"/>
+      <c r="A136" s="1" t="s">
+        <v>257</v>
+      </c>
       <c r="B136" s="1" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="137" spans="1:4">
       <c r="A137" s="6" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="138" spans="1:4">
+      <c r="A138" s="6"/>
       <c r="B138" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="C138" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="139" spans="1:4">
-      <c r="A139" s="6"/>
-      <c r="B139" s="4" t="s">
-        <v>261</v>
-      </c>
-      <c r="C139" s="4" t="s">
-        <v>258</v>
+      <c r="A139" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="B139" s="1" t="s">
+        <v>263</v>
       </c>
     </row>
     <row r="140" spans="1:4">
-      <c r="A140" s="7" t="s">
-        <v>262</v>
-      </c>
-      <c r="B140" s="6" t="s">
+      <c r="B140" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="C140" s="1" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4">
+      <c r="A141" s="6"/>
+      <c r="B141" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="C141" s="4" t="s">
         <v>263</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4">
+      <c r="A142" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="B142" s="6" t="s">
+        <v>268</v>
       </c>
     </row>
   </sheetData>
@@ -3741,67 +3801,67 @@
   <sheetData>
     <row r="1" ht="18" spans="1:3">
       <c r="A1" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
     </row>
     <row r="2" ht="18" spans="1:3">
       <c r="B2" s="1" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:3">
       <c r="B3" s="1" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:3">
       <c r="B4" s="1" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:3">
       <c r="B5" s="1" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:3">
       <c r="B6" s="1" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:3">
       <c r="A7" s="1" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:3">
       <c r="A8" s="1"/>
       <c r="B8" s="1" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="C8" s="1"/>
     </row>
@@ -3812,83 +3872,83 @@
     </row>
     <row r="10" ht="18" spans="1:3">
       <c r="A10" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
     </row>
     <row r="11" ht="18" spans="1:3">
       <c r="B11" s="1" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
     </row>
     <row r="13" ht="18" spans="1:3">
       <c r="A13" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
     </row>
     <row r="14" ht="18" spans="1:3">
       <c r="B14" s="1" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="C14" s="1"/>
     </row>
     <row r="15" ht="18" spans="1:3">
       <c r="B15" s="1" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="C15" s="1"/>
     </row>
     <row r="16" ht="18" spans="1:3">
       <c r="B16" s="1" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
     </row>
     <row r="17" ht="18" spans="1:4">
       <c r="B17" s="1" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="C17" s="1"/>
     </row>
     <row r="18" ht="18" spans="1:4">
       <c r="B18" s="1" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="C18" s="1"/>
     </row>
     <row r="19" ht="18" spans="1:4">
       <c r="B19" s="1" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="C19" s="1"/>
     </row>
     <row r="20" ht="18" spans="1:4">
       <c r="B20" s="1" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
     </row>
     <row r="21" ht="18" spans="1:4">
       <c r="B21" s="1" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
     </row>
     <row r="22" ht="18" spans="1:4">
@@ -3897,57 +3957,57 @@
     </row>
     <row r="23" ht="18" spans="1:4">
       <c r="A23" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="C23" s="1"/>
     </row>
     <row r="24" ht="18" spans="1:4">
       <c r="B24" s="1" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="C24" s="1"/>
     </row>
     <row r="25" ht="18" spans="1:4">
       <c r="B25" s="1" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
     </row>
     <row r="26" ht="18" spans="1:4">
       <c r="A26" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="D26" s="3"/>
     </row>
     <row r="27" ht="18" spans="1:4">
       <c r="A27" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="C27" s="1"/>
     </row>
     <row r="28" ht="18" spans="1:4">
       <c r="B28" s="1" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
     </row>
     <row r="29" ht="18" spans="1:4">
@@ -3956,68 +4016,68 @@
     </row>
     <row r="30" ht="18" spans="1:4">
       <c r="A30" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="C30" s="1"/>
     </row>
     <row r="31" ht="18" spans="1:4">
       <c r="B31" s="1" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="C31" s="1"/>
     </row>
     <row r="32" ht="18" spans="1:4">
       <c r="B32" s="1" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="C32" s="1"/>
     </row>
     <row r="33" ht="18" spans="1:4">
       <c r="B33" s="4" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="C33" s="1"/>
     </row>
     <row r="34" ht="18" spans="1:4">
       <c r="B34" s="4" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="C34" s="1"/>
     </row>
     <row r="35" ht="18" spans="1:4">
       <c r="B35" s="4" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
     </row>
     <row r="36" ht="18" spans="1:4">
       <c r="B36" s="4" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
     </row>
     <row r="37" ht="18" spans="1:4">
       <c r="B37" s="4" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
     </row>
     <row r="38" ht="18" spans="1:4">
@@ -4027,38 +4087,38 @@
     </row>
     <row r="39" ht="18" spans="1:4">
       <c r="A39" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="C39" s="1"/>
       <c r="D39" s="1"/>
     </row>
     <row r="40" ht="18" spans="1:4">
       <c r="B40" s="4" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="D40" s="1"/>
     </row>
     <row r="41" ht="18" spans="1:4">
       <c r="B41" s="4" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="D41" s="1"/>
     </row>
     <row r="42" ht="18" spans="1:4">
       <c r="B42" s="4" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="D42" s="1"/>
     </row>
@@ -4069,41 +4129,41 @@
     </row>
     <row r="44" ht="18" spans="1:4">
       <c r="A44" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="D44" s="1"/>
     </row>
     <row r="45" ht="18" spans="1:4">
       <c r="B45" s="1" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="D45" s="1"/>
     </row>
     <row r="46" ht="18" spans="1:4">
       <c r="B46" s="1" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="C46" s="4"/>
       <c r="D46" s="1"/>
     </row>
     <row r="47" ht="18" spans="1:4">
       <c r="A47" s="3" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="D47" s="1"/>
     </row>
@@ -4113,51 +4173,51 @@
     </row>
     <row r="49" ht="18" spans="1:5">
       <c r="A49" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="D49" s="5"/>
     </row>
     <row r="50" ht="18" spans="1:5">
       <c r="A50" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
     </row>
     <row r="51" ht="18" spans="1:5">
       <c r="B51" s="1" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="D51" s="1"/>
     </row>
     <row r="52" ht="18" spans="1:5">
       <c r="B52" s="1" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -4165,34 +4225,34 @@
     </row>
     <row r="54" ht="18" spans="1:5">
       <c r="A54" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
     </row>
     <row r="55" ht="18" spans="1:5">
       <c r="A55" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
     </row>
     <row r="57" ht="18" spans="1:5">
       <c r="A57" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
     </row>
     <row r="59" ht="18" spans="1:5">
       <c r="A59" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
     </row>
   </sheetData>

--- a/副词.xlsx
+++ b/副词.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="368">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="371">
   <si>
     <t>非常，一点也不</t>
   </si>
@@ -743,6 +743,46 @@
   </si>
   <si>
     <t>せっせと</t>
+  </si>
+  <si>
+    <r>
+      <t>勤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="128"/>
+      </rPr>
+      <t>奋地</t>
+    </r>
+  </si>
+  <si>
+    <t>まめに</t>
+  </si>
+  <si>
+    <r>
+      <t>まめに働く｜勤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="128"/>
+      </rPr>
+      <t>奋</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <charset val="128"/>
+      </rPr>
+      <t>工作</t>
+    </r>
   </si>
   <si>
     <r>
@@ -2618,7 +2658,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F142"/>
+  <dimension ref="A1:F143"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="16.1111111111111" style="1" customWidth="1"/>
@@ -3281,93 +3321,94 @@
       <c r="D79"/>
     </row>
     <row r="80" spans="1:6">
-      <c r="A80" s="7" t="s">
+      <c r="A80" s="1" t="s">
         <v>150</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="C80" s="1" t="s">
+      <c r="D80"/>
+      <c r="E80" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="D80"/>
     </row>
     <row r="81" spans="1:4">
+      <c r="A81" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>155</v>
+      </c>
       <c r="D81"/>
     </row>
     <row r="82" spans="1:4">
-      <c r="A82" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="B82" s="1" t="s">
+      <c r="D82"/>
+    </row>
+    <row r="83" spans="1:4">
+      <c r="A83" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="B83" s="1" t="s">
         <v>38</v>
-      </c>
-    </row>
-    <row r="83" spans="1:4">
-      <c r="B83" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="C83" s="1" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="84" spans="1:4">
       <c r="B84" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="85" spans="1:4">
-      <c r="A85" s="6" t="s">
-        <v>158</v>
-      </c>
       <c r="B85" s="1" t="s">
         <v>159</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="D85" s="1" t="s">
+    </row>
+    <row r="86" spans="1:4">
+      <c r="A86" s="6" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="86" spans="1:4">
       <c r="B86" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="D86" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4">
+      <c r="B87" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="C86" s="1" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="88" spans="1:4">
-      <c r="A88" s="6" t="s">
-        <v>163</v>
-      </c>
-      <c r="B88" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="C88" s="1" t="s">
+      <c r="C87" s="1" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="89" spans="1:4">
+      <c r="A89" s="6" t="s">
+        <v>166</v>
+      </c>
       <c r="B89" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="90" spans="1:4">
       <c r="B90" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="D90" s="1" t="s">
         <v>170</v>
       </c>
     </row>
@@ -3375,70 +3416,70 @@
       <c r="B91" s="1" t="s">
         <v>171</v>
       </c>
+      <c r="C91" s="1" t="s">
+        <v>172</v>
+      </c>
       <c r="D91" s="1" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="93" spans="1:4">
-      <c r="A93" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="B93" s="1" t="s">
+    </row>
+    <row r="92" spans="1:4">
+      <c r="B92" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="C93" s="1" t="s">
+      <c r="D92" s="1" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="94" spans="1:4">
-      <c r="A94" s="2"/>
+      <c r="A94" s="2" t="s">
+        <v>176</v>
+      </c>
       <c r="B94" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="95" spans="1:4">
-      <c r="A95" s="2" t="s">
-        <v>177</v>
-      </c>
+      <c r="A95" s="2"/>
       <c r="B95" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="96" spans="1:4">
-      <c r="A96" s="5" t="s">
-        <v>179</v>
+      <c r="A96" s="2" t="s">
+        <v>180</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="97" spans="1:4">
-      <c r="A97" s="5"/>
+      <c r="A97" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>183</v>
+      </c>
     </row>
     <row r="98" spans="1:4">
-      <c r="A98" s="5" t="s">
-        <v>181</v>
-      </c>
-      <c r="B98" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="C98" s="1" t="s">
-        <v>183</v>
-      </c>
+      <c r="A98" s="5"/>
     </row>
     <row r="99" spans="1:4">
-      <c r="A99" s="5"/>
+      <c r="A99" s="5" t="s">
+        <v>184</v>
+      </c>
       <c r="B99" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="100" spans="1:4">
-      <c r="A100" s="5" t="s">
-        <v>186</v>
-      </c>
+      <c r="A100" s="5"/>
       <c r="B100" s="1" t="s">
         <v>187</v>
       </c>
@@ -3447,146 +3488,146 @@
       </c>
     </row>
     <row r="101" spans="1:4">
-      <c r="A101" s="5"/>
+      <c r="A101" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>191</v>
+      </c>
     </row>
     <row r="102" spans="1:4">
-      <c r="A102" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="B102" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="C102" s="1" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="104" spans="1:4">
-      <c r="A104" s="6" t="s">
+      <c r="A102" s="5"/>
+    </row>
+    <row r="103" spans="1:4">
+      <c r="A103" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="B104" s="1" t="s">
+      <c r="B103" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="C104" s="1" t="s">
+      <c r="C103" s="1" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="106" spans="1:4">
-      <c r="A106" s="6" t="s">
+    <row r="105" spans="1:4">
+      <c r="A105" s="6" t="s">
         <v>195</v>
       </c>
-      <c r="B106" s="1" t="s">
+      <c r="B105" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="C106" s="1" t="s">
+      <c r="C105" s="1" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="108" spans="1:4">
-      <c r="A108" s="6" t="s">
+    <row r="107" spans="1:4">
+      <c r="A107" s="6" t="s">
         <v>198</v>
       </c>
-      <c r="B108" s="1" t="s">
+      <c r="B107" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4">
+      <c r="A109" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="B109" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="109" spans="1:4">
-      <c r="A109" s="6"/>
-      <c r="B109" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="C109" s="6" t="s">
-        <v>200</v>
-      </c>
-      <c r="D109" s="1" t="s">
-        <v>201</v>
-      </c>
-    </row>
     <row r="110" spans="1:4">
-      <c r="A110" s="6" t="s">
+      <c r="A110" s="6"/>
+      <c r="B110" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="B110" s="1" t="s">
+      <c r="C110" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="D110" s="1" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4">
+      <c r="A111" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="B111" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C110" s="1" t="s">
+      <c r="C111" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="111" spans="1:4">
-      <c r="A111" s="6"/>
-    </row>
     <row r="112" spans="1:4">
-      <c r="A112" s="6" t="s">
-        <v>203</v>
-      </c>
-      <c r="B112" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="C112" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="D112" s="1" t="s">
+      <c r="A112" s="6"/>
+    </row>
+    <row r="113" spans="1:4">
+      <c r="A113" s="6" t="s">
         <v>206</v>
       </c>
-    </row>
-    <row r="113" spans="1:3">
-      <c r="A113" s="6" t="s">
+      <c r="B113" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="B113" s="1" t="s">
+      <c r="C113" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="C113" s="1" t="s">
+      <c r="D113" s="1" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="114" spans="1:3">
+    <row r="114" spans="1:4">
       <c r="A114" s="6" t="s">
         <v>210</v>
       </c>
       <c r="B114" s="1" t="s">
         <v>211</v>
       </c>
-    </row>
-    <row r="116" spans="1:3">
-      <c r="A116" s="6" t="s">
+      <c r="C114" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="B116" s="1" t="s">
+    </row>
+    <row r="115" spans="1:4">
+      <c r="A115" s="6" t="s">
         <v>213</v>
       </c>
-      <c r="C116" s="1" t="s">
+      <c r="B115" s="1" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="117" spans="1:3">
-      <c r="A117" s="6"/>
-    </row>
-    <row r="118" spans="1:3">
-      <c r="A118" s="6" t="s">
+    <row r="117" spans="1:4">
+      <c r="A117" s="6" t="s">
         <v>215</v>
       </c>
-      <c r="B118" s="1" t="s">
+      <c r="B117" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="C118" s="1" t="s">
+      <c r="C117" s="1" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="119" spans="1:3">
-      <c r="A119" s="6"/>
+    <row r="118" spans="1:4">
+      <c r="A118" s="6"/>
+    </row>
+    <row r="119" spans="1:4">
+      <c r="A119" s="6" t="s">
+        <v>218</v>
+      </c>
       <c r="B119" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="120" spans="1:3">
-      <c r="A120" s="6" t="s">
         <v>220</v>
       </c>
+    </row>
+    <row r="120" spans="1:4">
+      <c r="A120" s="6"/>
       <c r="B120" s="1" t="s">
         <v>221</v>
       </c>
@@ -3594,95 +3635,95 @@
         <v>222</v>
       </c>
     </row>
-    <row r="121" spans="1:3">
-      <c r="A121" s="6"/>
-    </row>
-    <row r="122" spans="1:3">
-      <c r="A122" s="6" t="s">
+    <row r="121" spans="1:4">
+      <c r="A121" s="6" t="s">
         <v>223</v>
       </c>
-      <c r="B122" s="1" t="s">
+      <c r="B121" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="C122" s="1" t="s">
+      <c r="C121" s="1" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="123" spans="1:3">
-      <c r="A123" s="7" t="s">
+    <row r="122" spans="1:4">
+      <c r="A122" s="6"/>
+    </row>
+    <row r="123" spans="1:4">
+      <c r="A123" s="6" t="s">
         <v>226</v>
       </c>
-      <c r="B123" s="6" t="s">
+      <c r="B123" s="1" t="s">
         <v>227</v>
       </c>
-    </row>
-    <row r="124" spans="1:3">
-      <c r="A124" s="6" t="s">
+      <c r="C123" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="B124" s="1" t="s">
+    </row>
+    <row r="124" spans="1:4">
+      <c r="A124" s="7" t="s">
         <v>229</v>
       </c>
-    </row>
-    <row r="125" spans="1:3">
-      <c r="A125" s="1" t="s">
+      <c r="B124" s="6" t="s">
         <v>230</v>
       </c>
+    </row>
+    <row r="125" spans="1:4">
+      <c r="A125" s="6" t="s">
+        <v>231</v>
+      </c>
       <c r="B125" s="1" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="126" spans="1:3">
-      <c r="A126" s="6" t="s">
         <v>232</v>
       </c>
+    </row>
+    <row r="126" spans="1:4">
+      <c r="A126" s="1" t="s">
+        <v>233</v>
+      </c>
       <c r="B126" s="1" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="127" spans="1:3">
-      <c r="A127" s="4" t="s">
         <v>234</v>
       </c>
-      <c r="B127" s="4" t="s">
+    </row>
+    <row r="127" spans="1:4">
+      <c r="A127" s="6" t="s">
         <v>235</v>
       </c>
-      <c r="C127" s="4" t="s">
+      <c r="B127" s="1" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="128" spans="1:3">
+    <row r="128" spans="1:4">
       <c r="A128" s="4" t="s">
         <v>237</v>
       </c>
       <c r="B128" s="4" t="s">
         <v>238</v>
       </c>
+      <c r="C128" s="4" t="s">
+        <v>239</v>
+      </c>
     </row>
     <row r="129" spans="1:4">
-      <c r="A129" s="6" t="s">
-        <v>239</v>
-      </c>
-      <c r="B129" s="1" t="s">
+      <c r="A129" s="4" t="s">
         <v>240</v>
       </c>
+      <c r="B129" s="4" t="s">
+        <v>241</v>
+      </c>
     </row>
     <row r="130" spans="1:4">
-      <c r="A130" s="8" t="s">
-        <v>241</v>
-      </c>
-      <c r="B130" s="4" t="s">
+      <c r="A130" s="6" t="s">
         <v>242</v>
       </c>
+      <c r="B130" s="1" t="s">
+        <v>243</v>
+      </c>
     </row>
     <row r="131" spans="1:4">
-      <c r="A131" s="6" t="s">
-        <v>243</v>
-      </c>
-      <c r="B131" s="1" t="s">
+      <c r="A131" s="8" t="s">
         <v>244</v>
       </c>
-      <c r="C131" s="6" t="s">
+      <c r="B131" s="4" t="s">
         <v>245</v>
       </c>
     </row>
@@ -3693,93 +3734,104 @@
       <c r="B132" s="1" t="s">
         <v>247</v>
       </c>
+      <c r="C132" s="6" t="s">
+        <v>248</v>
+      </c>
     </row>
     <row r="133" spans="1:4">
-      <c r="A133" s="9" t="s">
-        <v>248</v>
+      <c r="A133" s="6" t="s">
+        <v>249</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="C133" s="6" t="s">
         <v>250</v>
       </c>
     </row>
     <row r="134" spans="1:4">
-      <c r="A134" s="6" t="s">
+      <c r="A134" s="9" t="s">
         <v>251</v>
       </c>
       <c r="B134" s="1" t="s">
         <v>252</v>
       </c>
+      <c r="C134" s="6" t="s">
+        <v>253</v>
+      </c>
     </row>
     <row r="135" spans="1:4">
-      <c r="A135" s="1" t="s">
-        <v>253</v>
+      <c r="A135" s="6" t="s">
+        <v>254</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="C135" s="1" t="s">
         <v>255</v>
-      </c>
-      <c r="D135" s="1" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="136" spans="1:4">
       <c r="A136" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B136" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="B136" s="1" t="s">
+      <c r="C136" s="1" t="s">
         <v>258</v>
       </c>
+      <c r="D136" s="1" t="s">
+        <v>259</v>
+      </c>
     </row>
     <row r="137" spans="1:4">
-      <c r="A137" s="6" t="s">
-        <v>259</v>
+      <c r="A137" s="1" t="s">
+        <v>260</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="138" spans="1:4">
-      <c r="A138" s="6"/>
+      <c r="A138" s="6" t="s">
+        <v>262</v>
+      </c>
       <c r="B138" s="1" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
     <row r="139" spans="1:4">
-      <c r="A139" s="6" t="s">
-        <v>262</v>
-      </c>
+      <c r="A139" s="6"/>
       <c r="B139" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="140" spans="1:4">
+      <c r="A140" s="6" t="s">
+        <v>265</v>
+      </c>
       <c r="B140" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="C140" s="1" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="141" spans="1:4">
-      <c r="A141" s="6"/>
-      <c r="B141" s="4" t="s">
+      <c r="B141" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="C141" s="1" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4">
+      <c r="A142" s="6"/>
+      <c r="B142" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="C142" s="4" t="s">
         <v>266</v>
       </c>
-      <c r="C141" s="4" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="142" spans="1:4">
-      <c r="A142" s="7" t="s">
-        <v>267</v>
-      </c>
-      <c r="B142" s="6" t="s">
-        <v>268</v>
+    </row>
+    <row r="143" spans="1:4">
+      <c r="A143" s="7" t="s">
+        <v>270</v>
+      </c>
+      <c r="B143" s="6" t="s">
+        <v>271</v>
       </c>
     </row>
   </sheetData>
@@ -3801,67 +3853,67 @@
   <sheetData>
     <row r="1" ht="18" spans="1:3">
       <c r="A1" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="2" ht="18" spans="1:3">
       <c r="B2" s="1" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:3">
       <c r="B3" s="1" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:3">
       <c r="B4" s="1" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:3">
       <c r="B5" s="1" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:3">
       <c r="B6" s="1" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:3">
       <c r="A7" s="1" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:3">
       <c r="A8" s="1"/>
       <c r="B8" s="1" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="C8" s="1"/>
     </row>
@@ -3872,83 +3924,83 @@
     </row>
     <row r="10" ht="18" spans="1:3">
       <c r="A10" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="11" ht="18" spans="1:3">
       <c r="B11" s="1" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="13" ht="18" spans="1:3">
       <c r="A13" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
     <row r="14" ht="18" spans="1:3">
       <c r="B14" s="1" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="C14" s="1"/>
     </row>
     <row r="15" ht="18" spans="1:3">
       <c r="B15" s="1" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="C15" s="1"/>
     </row>
     <row r="16" ht="18" spans="1:3">
       <c r="B16" s="1" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="17" ht="18" spans="1:4">
       <c r="B17" s="1" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="C17" s="1"/>
     </row>
     <row r="18" ht="18" spans="1:4">
       <c r="B18" s="1" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="C18" s="1"/>
     </row>
     <row r="19" ht="18" spans="1:4">
       <c r="B19" s="1" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="C19" s="1"/>
     </row>
     <row r="20" ht="18" spans="1:4">
       <c r="B20" s="1" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
     <row r="21" ht="18" spans="1:4">
       <c r="B21" s="1" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
     </row>
     <row r="22" ht="18" spans="1:4">
@@ -3957,57 +4009,57 @@
     </row>
     <row r="23" ht="18" spans="1:4">
       <c r="A23" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="C23" s="1"/>
     </row>
     <row r="24" ht="18" spans="1:4">
       <c r="B24" s="1" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="C24" s="1"/>
     </row>
     <row r="25" ht="18" spans="1:4">
       <c r="B25" s="1" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="26" ht="18" spans="1:4">
       <c r="A26" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="D26" s="3"/>
     </row>
     <row r="27" ht="18" spans="1:4">
       <c r="A27" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="C27" s="1"/>
     </row>
     <row r="28" ht="18" spans="1:4">
       <c r="B28" s="1" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="29" ht="18" spans="1:4">
@@ -4016,68 +4068,68 @@
     </row>
     <row r="30" ht="18" spans="1:4">
       <c r="A30" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="C30" s="1"/>
     </row>
     <row r="31" ht="18" spans="1:4">
       <c r="B31" s="1" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="C31" s="1"/>
     </row>
     <row r="32" ht="18" spans="1:4">
       <c r="B32" s="1" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="C32" s="1"/>
     </row>
     <row r="33" ht="18" spans="1:4">
       <c r="B33" s="4" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="C33" s="1"/>
     </row>
     <row r="34" ht="18" spans="1:4">
       <c r="B34" s="4" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="C34" s="1"/>
     </row>
     <row r="35" ht="18" spans="1:4">
       <c r="B35" s="4" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
     </row>
     <row r="36" ht="18" spans="1:4">
       <c r="B36" s="4" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
     </row>
     <row r="37" ht="18" spans="1:4">
       <c r="B37" s="4" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
     </row>
     <row r="38" ht="18" spans="1:4">
@@ -4087,38 +4139,38 @@
     </row>
     <row r="39" ht="18" spans="1:4">
       <c r="A39" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="C39" s="1"/>
       <c r="D39" s="1"/>
     </row>
     <row r="40" ht="18" spans="1:4">
       <c r="B40" s="4" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="D40" s="1"/>
     </row>
     <row r="41" ht="18" spans="1:4">
       <c r="B41" s="4" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="D41" s="1"/>
     </row>
     <row r="42" ht="18" spans="1:4">
       <c r="B42" s="4" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="D42" s="1"/>
     </row>
@@ -4129,41 +4181,41 @@
     </row>
     <row r="44" ht="18" spans="1:4">
       <c r="A44" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="D44" s="1"/>
     </row>
     <row r="45" ht="18" spans="1:4">
       <c r="B45" s="1" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="D45" s="1"/>
     </row>
     <row r="46" ht="18" spans="1:4">
       <c r="B46" s="1" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="C46" s="4"/>
       <c r="D46" s="1"/>
     </row>
     <row r="47" ht="18" spans="1:4">
       <c r="A47" s="3" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="D47" s="1"/>
     </row>
@@ -4173,51 +4225,51 @@
     </row>
     <row r="49" ht="18" spans="1:5">
       <c r="A49" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="D49" s="5"/>
     </row>
     <row r="50" ht="18" spans="1:5">
       <c r="A50" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
     </row>
     <row r="51" ht="18" spans="1:5">
       <c r="B51" s="1" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="D51" s="1"/>
     </row>
     <row r="52" ht="18" spans="1:5">
       <c r="B52" s="1" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -4225,34 +4277,34 @@
     </row>
     <row r="54" ht="18" spans="1:5">
       <c r="A54" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
     <row r="55" ht="18" spans="1:5">
       <c r="A55" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="57" ht="18" spans="1:5">
       <c r="A57" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
     </row>
     <row r="59" ht="18" spans="1:5">
       <c r="A59" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
     </row>
   </sheetData>

--- a/副词.xlsx
+++ b/副词.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="371">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="380">
   <si>
     <t>非常，一点也不</t>
   </si>
@@ -462,6 +462,12 @@
   </si>
   <si>
     <t>確か</t>
+  </si>
+  <si>
+    <t>まさに</t>
+  </si>
+  <si>
+    <t>正に</t>
   </si>
   <si>
     <t>理所应当</t>
@@ -746,6 +752,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <charset val="128"/>
+      </rPr>
       <t>勤</t>
     </r>
     <r>
@@ -763,6 +775,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <charset val="128"/>
+      </rPr>
       <t>まめに働く｜勤</t>
     </r>
     <r>
@@ -923,6 +941,53 @@
     <t>（赶快）</t>
   </si>
   <si>
+    <t>哪怕...也好，至少</t>
+  </si>
+  <si>
+    <t>せめて</t>
+  </si>
+  <si>
+    <r>
+      <t>せめてこれだけはもらいたい｜至少也</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="128"/>
+      </rPr>
+      <t>给</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <charset val="128"/>
+      </rPr>
+      <t>我</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="128"/>
+      </rPr>
+      <t>这</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <charset val="128"/>
+      </rPr>
+      <t>个</t>
+    </r>
+  </si>
+  <si>
     <t>除此之外</t>
   </si>
   <si>
@@ -1006,6 +1071,12 @@
     <t>主に</t>
   </si>
   <si>
+    <t>充足的</t>
+  </si>
+  <si>
+    <t>たっぷり</t>
+  </si>
+  <si>
     <t>不够的</t>
   </si>
   <si>
@@ -1260,6 +1331,12 @@
   </si>
   <si>
     <t>ゆったり</t>
+  </si>
+  <si>
+    <t>一下子地，立刻</t>
+  </si>
+  <si>
+    <t>すっと</t>
   </si>
   <si>
     <t>但是</t>
@@ -2658,7 +2735,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F143"/>
+  <dimension ref="A1:F147"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="16.1111111111111" style="1" customWidth="1"/>
@@ -3083,48 +3160,49 @@
       </c>
     </row>
     <row r="50" spans="1:3">
-      <c r="A50" s="6" t="s">
+      <c r="A50" s="6"/>
+      <c r="B50" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="B50" s="1" t="s">
+      <c r="C50" s="1" t="s">
         <v>98</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="B51" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="B51" s="1" t="s">
+      <c r="C51" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="C51" s="1" t="s">
+    </row>
+    <row r="52" spans="1:3">
+      <c r="A52" s="6" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="52" spans="1:3">
-      <c r="A52" s="6"/>
+      <c r="B52" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="53" spans="1:3">
-      <c r="A53" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>104</v>
-      </c>
+      <c r="A53" s="6"/>
     </row>
     <row r="54" spans="1:3">
-      <c r="A54" s="6"/>
+      <c r="A54" s="6" t="s">
+        <v>105</v>
+      </c>
       <c r="B54" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="C54" s="1" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="55" spans="1:3">
+      <c r="A55" s="6"/>
       <c r="B55" s="1" t="s">
         <v>107</v>
       </c>
@@ -3132,56 +3210,56 @@
         <v>108</v>
       </c>
     </row>
-    <row r="57" spans="1:3">
-      <c r="A57" s="6" t="s">
+    <row r="56" spans="1:3">
+      <c r="B56" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="B57" s="1" t="s">
+      <c r="C56" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="C57" s="1" t="s">
+    </row>
+    <row r="58" spans="1:3">
+      <c r="A58" s="6" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="58" spans="1:3">
-      <c r="A58" s="6"/>
+      <c r="B58" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>113</v>
+      </c>
     </row>
     <row r="59" spans="1:3">
-      <c r="A59" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="C59" s="1" t="s">
+      <c r="A59" s="6"/>
+    </row>
+    <row r="60" spans="1:3">
+      <c r="A60" s="6" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="60" spans="1:3">
-      <c r="A60" s="6"/>
       <c r="B60" s="1" t="s">
         <v>115</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61" s="6"/>
       <c r="B61" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="C61" s="1" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62" s="6"/>
+      <c r="B62" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>119</v>
+      </c>
     </row>
     <row r="63" spans="1:3">
-      <c r="A63" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>119</v>
-      </c>
+      <c r="A63" s="6"/>
     </row>
     <row r="64" spans="1:3">
       <c r="A64" s="6" t="s">
@@ -3198,83 +3276,82 @@
       <c r="B65" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="C65" s="1" t="s">
-        <v>124</v>
-      </c>
     </row>
     <row r="66" spans="1:6">
       <c r="A66" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="B66" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="B66" s="1" t="s">
+      <c r="C66" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="E66" s="1" t="s">
+    </row>
+    <row r="67" spans="1:6">
+      <c r="A67" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="F66" s="1" t="s">
+      <c r="B67" s="1" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="68" spans="1:6">
-      <c r="A68" s="6" t="s">
+      <c r="E67" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="B68" s="1" t="s">
+      <c r="F67" s="1" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="69" spans="1:6">
+      <c r="A69" s="6" t="s">
+        <v>131</v>
+      </c>
       <c r="B69" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="C69" s="1" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="71" spans="1:6">
-      <c r="A71" s="6" t="s">
+    <row r="70" spans="1:6">
+      <c r="B70" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="B71" s="1" t="s">
+      <c r="C70" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="C71" s="1" t="s">
+    </row>
+    <row r="72" spans="1:6">
+      <c r="A72" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="D71" s="3" t="s">
+      <c r="B72" s="1" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="72" spans="1:6">
-      <c r="A72" s="6"/>
-      <c r="B72" s="1" t="s">
+      <c r="C72" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="D72" s="3"/>
+      <c r="D72" s="3" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="73" spans="1:6">
+      <c r="A73" s="6"/>
       <c r="B73" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="C73" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="D73"/>
-      <c r="F73"/>
+      <c r="D73" s="3"/>
     </row>
     <row r="74" spans="1:6">
       <c r="B74" s="1" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D74"/>
+      <c r="F74"/>
     </row>
     <row r="75" spans="1:6">
       <c r="B75" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>142</v>
@@ -3283,39 +3360,39 @@
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="1" t="s">
-        <v>63</v>
+        <v>143</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>64</v>
+        <v>144</v>
       </c>
       <c r="D76"/>
     </row>
     <row r="77" spans="1:6">
       <c r="B77" s="1" t="s">
-        <v>143</v>
+        <v>63</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>144</v>
+        <v>64</v>
       </c>
       <c r="D77"/>
     </row>
     <row r="78" spans="1:6">
-      <c r="A78" s="1" t="s">
+      <c r="B78" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="B78" s="1" t="s">
+      <c r="C78" s="1" t="s">
         <v>146</v>
-      </c>
-      <c r="C78" s="1" t="s">
-        <v>147</v>
       </c>
       <c r="D78"/>
     </row>
     <row r="79" spans="1:6">
       <c r="A79" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B79" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="B79" s="1" t="s">
+      <c r="C79" s="1" t="s">
         <v>149</v>
       </c>
       <c r="D79"/>
@@ -3328,42 +3405,43 @@
         <v>151</v>
       </c>
       <c r="D80"/>
-      <c r="E80" s="1" t="s">
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81" s="1" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="81" spans="1:4">
-      <c r="A81" s="7" t="s">
+      <c r="B81" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="B81" s="1" t="s">
+      <c r="D81"/>
+      <c r="E81" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="C81" s="1" t="s">
+    </row>
+    <row r="82" spans="1:5">
+      <c r="A82" s="7" t="s">
         <v>155</v>
       </c>
-      <c r="D81"/>
-    </row>
-    <row r="82" spans="1:4">
+      <c r="B82" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>157</v>
+      </c>
       <c r="D82"/>
     </row>
-    <row r="83" spans="1:4">
-      <c r="A83" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="B83" s="1" t="s">
+    <row r="83" spans="1:5">
+      <c r="D83"/>
+    </row>
+    <row r="84" spans="1:5">
+      <c r="A84" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="B84" s="1" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="84" spans="1:4">
-      <c r="B84" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="C84" s="1" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="85" spans="1:4">
+    <row r="85" spans="1:5">
       <c r="B85" s="1" t="s">
         <v>159</v>
       </c>
@@ -3371,40 +3449,40 @@
         <v>160</v>
       </c>
     </row>
-    <row r="86" spans="1:4">
-      <c r="A86" s="6" t="s">
+    <row r="86" spans="1:5">
+      <c r="B86" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="B86" s="1" t="s">
+      <c r="C86" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="C86" s="1" t="s">
+    </row>
+    <row r="87" spans="1:5">
+      <c r="A87" s="6" t="s">
         <v>163</v>
       </c>
-      <c r="D86" s="1" t="s">
+      <c r="B87" s="1" t="s">
         <v>164</v>
-      </c>
-    </row>
-    <row r="87" spans="1:4">
-      <c r="B87" s="1" t="s">
-        <v>141</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>165</v>
       </c>
-    </row>
-    <row r="89" spans="1:4">
-      <c r="A89" s="6" t="s">
+      <c r="D87" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="B89" s="1" t="s">
+    </row>
+    <row r="88" spans="1:5">
+      <c r="B88" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C88" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="C89" s="1" t="s">
+    </row>
+    <row r="90" spans="1:5">
+      <c r="A90" s="6" t="s">
         <v>168</v>
       </c>
-    </row>
-    <row r="90" spans="1:4">
       <c r="B90" s="1" t="s">
         <v>169</v>
       </c>
@@ -3412,82 +3490,81 @@
         <v>170</v>
       </c>
     </row>
-    <row r="91" spans="1:4">
+    <row r="91" spans="1:5">
       <c r="B91" s="1" t="s">
         <v>171</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="D91" s="1" t="s">
+    </row>
+    <row r="92" spans="1:5">
+      <c r="B92" s="1" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="92" spans="1:4">
-      <c r="B92" s="1" t="s">
+      <c r="C92" s="1" t="s">
         <v>174</v>
       </c>
       <c r="D92" s="1" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="94" spans="1:4">
-      <c r="A94" s="2" t="s">
+    <row r="93" spans="1:5">
+      <c r="B93" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="B94" s="1" t="s">
+      <c r="D93" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="C94" s="1" t="s">
+    </row>
+    <row r="95" spans="1:5">
+      <c r="A95" s="1" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="95" spans="1:4">
-      <c r="A95" s="2"/>
       <c r="B95" s="1" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="96" spans="1:4">
+      <c r="D95" s="1" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5">
       <c r="A96" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="97" spans="1:4">
-      <c r="A97" s="5" t="s">
         <v>182</v>
       </c>
+      <c r="C96" s="1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3">
+      <c r="A97" s="2"/>
       <c r="B97" s="1" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="98" spans="1:4">
-      <c r="A98" s="5"/>
-    </row>
-    <row r="99" spans="1:4">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3">
+      <c r="A98" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3">
       <c r="A99" s="5" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="C99" s="1" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="100" spans="1:4">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3">
       <c r="A100" s="5"/>
-      <c r="B100" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="C100" s="1" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="101" spans="1:4">
+    </row>
+    <row r="101" spans="1:3">
       <c r="A101" s="5" t="s">
         <v>189</v>
       </c>
@@ -3498,216 +3575,217 @@
         <v>191</v>
       </c>
     </row>
-    <row r="102" spans="1:4">
+    <row r="102" spans="1:3">
       <c r="A102" s="5"/>
-    </row>
-    <row r="103" spans="1:4">
-      <c r="A103" s="2" t="s">
+      <c r="B102" s="1" t="s">
         <v>192</v>
       </c>
+      <c r="C102" s="1" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3">
+      <c r="A103" s="5" t="s">
+        <v>194</v>
+      </c>
       <c r="B103" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="105" spans="1:4">
-      <c r="A105" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3">
+      <c r="A104" s="5"/>
+    </row>
+    <row r="105" spans="1:3">
+      <c r="A105" s="2" t="s">
+        <v>197</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="107" spans="1:4">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3">
       <c r="A107" s="6" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="109" spans="1:4">
-      <c r="A109" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3">
+      <c r="A109" s="1" t="s">
+        <v>203</v>
       </c>
       <c r="B109" s="1" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3">
+      <c r="A110" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3">
+      <c r="A112" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="B112" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="110" spans="1:4">
-      <c r="A110" s="6"/>
-      <c r="B110" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="C110" s="6" t="s">
-        <v>203</v>
-      </c>
-      <c r="D110" s="1" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="111" spans="1:4">
-      <c r="A111" s="6" t="s">
-        <v>205</v>
-      </c>
-      <c r="B111" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C111" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="112" spans="1:4">
-      <c r="A112" s="6"/>
-    </row>
     <row r="113" spans="1:4">
-      <c r="A113" s="6" t="s">
-        <v>206</v>
-      </c>
+      <c r="A113" s="6"/>
       <c r="B113" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="C113" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
+      </c>
+      <c r="C113" s="6" t="s">
+        <v>210</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="114" spans="1:4">
       <c r="A114" s="6" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>211</v>
+        <v>27</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>212</v>
+        <v>28</v>
       </c>
     </row>
     <row r="115" spans="1:4">
-      <c r="A115" s="6" t="s">
+      <c r="A115" s="6"/>
+    </row>
+    <row r="116" spans="1:4">
+      <c r="A116" s="6" t="s">
         <v>213</v>
       </c>
-      <c r="B115" s="1" t="s">
+      <c r="B116" s="1" t="s">
         <v>214</v>
+      </c>
+      <c r="C116" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="D116" s="1" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="117" spans="1:4">
       <c r="A117" s="6" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="118" spans="1:4">
-      <c r="A118" s="6"/>
-    </row>
-    <row r="119" spans="1:4">
-      <c r="A119" s="6" t="s">
-        <v>218</v>
-      </c>
-      <c r="B119" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="C119" s="1" t="s">
+      <c r="A118" s="6" t="s">
         <v>220</v>
       </c>
+      <c r="B118" s="1" t="s">
+        <v>221</v>
+      </c>
     </row>
     <row r="120" spans="1:4">
-      <c r="A120" s="6"/>
+      <c r="A120" s="6" t="s">
+        <v>222</v>
+      </c>
       <c r="B120" s="1" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="121" spans="1:4">
-      <c r="A121" s="6" t="s">
-        <v>223</v>
-      </c>
-      <c r="B121" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="C121" s="1" t="s">
+      <c r="A121" s="6"/>
+    </row>
+    <row r="122" spans="1:4">
+      <c r="A122" s="6" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="122" spans="1:4">
-      <c r="A122" s="6"/>
+      <c r="B122" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="C122" s="1" t="s">
+        <v>227</v>
+      </c>
     </row>
     <row r="123" spans="1:4">
-      <c r="A123" s="6" t="s">
-        <v>226</v>
-      </c>
+      <c r="A123" s="6"/>
       <c r="B123" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="124" spans="1:4">
-      <c r="A124" s="7" t="s">
-        <v>229</v>
-      </c>
-      <c r="B124" s="6" t="s">
+      <c r="A124" s="6" t="s">
         <v>230</v>
       </c>
+      <c r="B124" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="C124" s="1" t="s">
+        <v>232</v>
+      </c>
     </row>
     <row r="125" spans="1:4">
-      <c r="A125" s="6" t="s">
-        <v>231</v>
-      </c>
-      <c r="B125" s="1" t="s">
-        <v>232</v>
-      </c>
+      <c r="A125" s="6"/>
     </row>
     <row r="126" spans="1:4">
-      <c r="A126" s="1" t="s">
+      <c r="A126" s="6" t="s">
         <v>233</v>
       </c>
       <c r="B126" s="1" t="s">
         <v>234</v>
       </c>
+      <c r="C126" s="1" t="s">
+        <v>235</v>
+      </c>
     </row>
     <row r="127" spans="1:4">
-      <c r="A127" s="6" t="s">
-        <v>235</v>
-      </c>
-      <c r="B127" s="1" t="s">
+      <c r="A127" s="7" t="s">
         <v>236</v>
       </c>
+      <c r="B127" s="6" t="s">
+        <v>237</v>
+      </c>
     </row>
     <row r="128" spans="1:4">
-      <c r="A128" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="B128" s="4" t="s">
+      <c r="A128" s="6" t="s">
         <v>238</v>
       </c>
-      <c r="C128" s="4" t="s">
+      <c r="B128" s="1" t="s">
         <v>239</v>
       </c>
     </row>
     <row r="129" spans="1:4">
-      <c r="A129" s="4" t="s">
+      <c r="A129" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="B129" s="4" t="s">
+      <c r="B129" s="1" t="s">
         <v>241</v>
       </c>
     </row>
@@ -3720,21 +3798,21 @@
       </c>
     </row>
     <row r="131" spans="1:4">
-      <c r="A131" s="8" t="s">
+      <c r="A131" s="4" t="s">
         <v>244</v>
       </c>
       <c r="B131" s="4" t="s">
         <v>245</v>
       </c>
+      <c r="C131" s="4" t="s">
+        <v>246</v>
+      </c>
     </row>
     <row r="132" spans="1:4">
-      <c r="A132" s="6" t="s">
-        <v>246</v>
-      </c>
-      <c r="B132" s="1" t="s">
+      <c r="A132" s="4" t="s">
         <v>247</v>
       </c>
-      <c r="C132" s="6" t="s">
+      <c r="B132" s="4" t="s">
         <v>248</v>
       </c>
     </row>
@@ -3747,91 +3825,126 @@
       </c>
     </row>
     <row r="134" spans="1:4">
-      <c r="A134" s="9" t="s">
+      <c r="A134" s="8" t="s">
         <v>251</v>
       </c>
-      <c r="B134" s="1" t="s">
+      <c r="B134" s="4" t="s">
         <v>252</v>
-      </c>
-      <c r="C134" s="6" t="s">
-        <v>253</v>
       </c>
     </row>
     <row r="135" spans="1:4">
       <c r="A135" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="B135" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="B135" s="1" t="s">
+      <c r="C135" s="6" t="s">
         <v>255</v>
       </c>
     </row>
     <row r="136" spans="1:4">
-      <c r="A136" s="1" t="s">
+      <c r="A136" s="6" t="s">
         <v>256</v>
       </c>
       <c r="B136" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="C136" s="1" t="s">
+    </row>
+    <row r="137" spans="1:4">
+      <c r="A137" s="9" t="s">
         <v>258</v>
       </c>
-      <c r="D136" s="1" t="s">
+      <c r="B137" s="1" t="s">
         <v>259</v>
       </c>
-    </row>
-    <row r="137" spans="1:4">
-      <c r="A137" s="1" t="s">
+      <c r="C137" s="6" t="s">
         <v>260</v>
-      </c>
-      <c r="B137" s="1" t="s">
-        <v>261</v>
       </c>
     </row>
     <row r="138" spans="1:4">
       <c r="A138" s="6" t="s">
+        <v>261</v>
+      </c>
+      <c r="B138" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="B138" s="1" t="s">
+    </row>
+    <row r="139" spans="1:4">
+      <c r="A139" s="1" t="s">
         <v>263</v>
       </c>
-    </row>
-    <row r="139" spans="1:4">
-      <c r="A139" s="6"/>
       <c r="B139" s="1" t="s">
         <v>264</v>
       </c>
+      <c r="C139" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="D139" s="1" t="s">
+        <v>266</v>
+      </c>
     </row>
     <row r="140" spans="1:4">
-      <c r="A140" s="6" t="s">
-        <v>265</v>
+      <c r="A140" s="1" t="s">
+        <v>267</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="141" spans="1:4">
+      <c r="A141" s="6" t="s">
+        <v>269</v>
+      </c>
       <c r="B141" s="1" t="s">
-        <v>267</v>
-      </c>
-      <c r="C141" s="1" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="142" spans="1:4">
       <c r="A142" s="6"/>
-      <c r="B142" s="4" t="s">
-        <v>269</v>
-      </c>
-      <c r="C142" s="4" t="s">
-        <v>266</v>
+      <c r="B142" s="1" t="s">
+        <v>271</v>
       </c>
     </row>
     <row r="143" spans="1:4">
-      <c r="A143" s="7" t="s">
-        <v>270</v>
-      </c>
-      <c r="B143" s="6" t="s">
-        <v>271</v>
+      <c r="A143" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="B143" s="1" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4">
+      <c r="B144" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="C144" s="1" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3">
+      <c r="A145" s="6"/>
+      <c r="B145" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="C145" s="4" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3">
+      <c r="A146" s="7" t="s">
+        <v>277</v>
+      </c>
+      <c r="B146" s="6" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3">
+      <c r="A147" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="B147" s="1" t="s">
+        <v>280</v>
       </c>
     </row>
   </sheetData>
@@ -3853,67 +3966,67 @@
   <sheetData>
     <row r="1" ht="18" spans="1:3">
       <c r="A1" t="s">
-        <v>272</v>
+        <v>281</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>273</v>
+        <v>282</v>
       </c>
     </row>
     <row r="2" ht="18" spans="1:3">
       <c r="B2" s="1" t="s">
-        <v>274</v>
+        <v>283</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>275</v>
+        <v>284</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:3">
       <c r="B3" s="1" t="s">
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>277</v>
+        <v>286</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:3">
       <c r="B4" s="1" t="s">
-        <v>278</v>
+        <v>287</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>279</v>
+        <v>288</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:3">
       <c r="B5" s="1" t="s">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>281</v>
+        <v>290</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:3">
       <c r="B6" s="1" t="s">
-        <v>282</v>
+        <v>291</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>283</v>
+        <v>292</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:3">
       <c r="A7" s="1" t="s">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>285</v>
+        <v>294</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>286</v>
+        <v>295</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:3">
       <c r="A8" s="1"/>
       <c r="B8" s="1" t="s">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="C8" s="1"/>
     </row>
@@ -3924,83 +4037,83 @@
     </row>
     <row r="10" ht="18" spans="1:3">
       <c r="A10" t="s">
-        <v>288</v>
+        <v>297</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>289</v>
+        <v>298</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>290</v>
+        <v>299</v>
       </c>
     </row>
     <row r="11" ht="18" spans="1:3">
       <c r="B11" s="1" t="s">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>292</v>
+        <v>301</v>
       </c>
     </row>
     <row r="13" ht="18" spans="1:3">
       <c r="A13" t="s">
-        <v>293</v>
+        <v>302</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
     </row>
     <row r="14" ht="18" spans="1:3">
       <c r="B14" s="1" t="s">
-        <v>295</v>
+        <v>304</v>
       </c>
       <c r="C14" s="1"/>
     </row>
     <row r="15" ht="18" spans="1:3">
       <c r="B15" s="1" t="s">
-        <v>296</v>
+        <v>305</v>
       </c>
       <c r="C15" s="1"/>
     </row>
     <row r="16" ht="18" spans="1:3">
       <c r="B16" s="1" t="s">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>298</v>
+        <v>307</v>
       </c>
     </row>
     <row r="17" ht="18" spans="1:4">
       <c r="B17" s="1" t="s">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="C17" s="1"/>
     </row>
     <row r="18" ht="18" spans="1:4">
       <c r="B18" s="1" t="s">
-        <v>300</v>
+        <v>309</v>
       </c>
       <c r="C18" s="1"/>
     </row>
     <row r="19" ht="18" spans="1:4">
       <c r="B19" s="1" t="s">
-        <v>301</v>
+        <v>310</v>
       </c>
       <c r="C19" s="1"/>
     </row>
     <row r="20" ht="18" spans="1:4">
       <c r="B20" s="1" t="s">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>303</v>
+        <v>312</v>
       </c>
     </row>
     <row r="21" ht="18" spans="1:4">
       <c r="B21" s="1" t="s">
-        <v>304</v>
+        <v>313</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>305</v>
+        <v>314</v>
       </c>
     </row>
     <row r="22" ht="18" spans="1:4">
@@ -4009,57 +4122,57 @@
     </row>
     <row r="23" ht="18" spans="1:4">
       <c r="A23" t="s">
-        <v>306</v>
+        <v>315</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>307</v>
+        <v>316</v>
       </c>
       <c r="C23" s="1"/>
     </row>
     <row r="24" ht="18" spans="1:4">
       <c r="B24" s="1" t="s">
-        <v>308</v>
+        <v>317</v>
       </c>
       <c r="C24" s="1"/>
     </row>
     <row r="25" ht="18" spans="1:4">
       <c r="B25" s="1" t="s">
-        <v>309</v>
+        <v>318</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>310</v>
+        <v>319</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>311</v>
+        <v>320</v>
       </c>
     </row>
     <row r="26" ht="18" spans="1:4">
       <c r="A26" t="s">
-        <v>312</v>
+        <v>321</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>313</v>
+        <v>322</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>314</v>
+        <v>323</v>
       </c>
       <c r="D26" s="3"/>
     </row>
     <row r="27" ht="18" spans="1:4">
       <c r="A27" t="s">
-        <v>315</v>
+        <v>324</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>316</v>
+        <v>325</v>
       </c>
       <c r="C27" s="1"/>
     </row>
     <row r="28" ht="18" spans="1:4">
       <c r="B28" s="1" t="s">
-        <v>317</v>
+        <v>326</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>318</v>
+        <v>327</v>
       </c>
     </row>
     <row r="29" ht="18" spans="1:4">
@@ -4068,68 +4181,68 @@
     </row>
     <row r="30" ht="18" spans="1:4">
       <c r="A30" t="s">
-        <v>319</v>
+        <v>328</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="C30" s="1"/>
     </row>
     <row r="31" ht="18" spans="1:4">
       <c r="B31" s="1" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="C31" s="1"/>
     </row>
     <row r="32" ht="18" spans="1:4">
       <c r="B32" s="1" t="s">
-        <v>322</v>
+        <v>331</v>
       </c>
       <c r="C32" s="1"/>
     </row>
     <row r="33" ht="18" spans="1:4">
       <c r="B33" s="4" t="s">
-        <v>323</v>
+        <v>332</v>
       </c>
       <c r="C33" s="1"/>
     </row>
     <row r="34" ht="18" spans="1:4">
       <c r="B34" s="4" t="s">
-        <v>324</v>
+        <v>333</v>
       </c>
       <c r="C34" s="1"/>
     </row>
     <row r="35" ht="18" spans="1:4">
       <c r="B35" s="4" t="s">
-        <v>325</v>
+        <v>334</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>326</v>
+        <v>335</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>327</v>
+        <v>336</v>
       </c>
     </row>
     <row r="36" ht="18" spans="1:4">
       <c r="B36" s="4" t="s">
-        <v>328</v>
+        <v>337</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>329</v>
+        <v>338</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>330</v>
+        <v>339</v>
       </c>
     </row>
     <row r="37" ht="18" spans="1:4">
       <c r="B37" s="4" t="s">
-        <v>331</v>
+        <v>340</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>333</v>
+        <v>342</v>
       </c>
     </row>
     <row r="38" ht="18" spans="1:4">
@@ -4139,38 +4252,38 @@
     </row>
     <row r="39" ht="18" spans="1:4">
       <c r="A39" t="s">
-        <v>334</v>
+        <v>343</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>335</v>
+        <v>344</v>
       </c>
       <c r="C39" s="1"/>
       <c r="D39" s="1"/>
     </row>
     <row r="40" ht="18" spans="1:4">
       <c r="B40" s="4" t="s">
-        <v>336</v>
+        <v>345</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>337</v>
+        <v>346</v>
       </c>
       <c r="D40" s="1"/>
     </row>
     <row r="41" ht="18" spans="1:4">
       <c r="B41" s="4" t="s">
-        <v>338</v>
+        <v>347</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>326</v>
+        <v>335</v>
       </c>
       <c r="D41" s="1"/>
     </row>
     <row r="42" ht="18" spans="1:4">
       <c r="B42" s="4" t="s">
-        <v>339</v>
+        <v>348</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>340</v>
+        <v>349</v>
       </c>
       <c r="D42" s="1"/>
     </row>
@@ -4181,41 +4294,41 @@
     </row>
     <row r="44" ht="18" spans="1:4">
       <c r="A44" t="s">
-        <v>341</v>
+        <v>350</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>342</v>
+        <v>351</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>343</v>
+        <v>352</v>
       </c>
       <c r="D44" s="1"/>
     </row>
     <row r="45" ht="18" spans="1:4">
       <c r="B45" s="1" t="s">
-        <v>344</v>
+        <v>353</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>345</v>
+        <v>354</v>
       </c>
       <c r="D45" s="1"/>
     </row>
     <row r="46" ht="18" spans="1:4">
       <c r="B46" s="1" t="s">
-        <v>346</v>
+        <v>355</v>
       </c>
       <c r="C46" s="4"/>
       <c r="D46" s="1"/>
     </row>
     <row r="47" ht="18" spans="1:4">
       <c r="A47" s="3" t="s">
-        <v>347</v>
+        <v>356</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>348</v>
+        <v>357</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>349</v>
+        <v>358</v>
       </c>
       <c r="D47" s="1"/>
     </row>
@@ -4225,51 +4338,51 @@
     </row>
     <row r="49" ht="18" spans="1:5">
       <c r="A49" t="s">
-        <v>350</v>
+        <v>359</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>351</v>
+        <v>360</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>352</v>
+        <v>361</v>
       </c>
       <c r="D49" s="5"/>
     </row>
     <row r="50" ht="18" spans="1:5">
       <c r="A50" t="s">
-        <v>353</v>
+        <v>362</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>354</v>
+        <v>363</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>355</v>
+        <v>364</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>356</v>
+        <v>365</v>
       </c>
     </row>
     <row r="51" ht="18" spans="1:5">
       <c r="B51" s="1" t="s">
-        <v>357</v>
+        <v>366</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>358</v>
+        <v>367</v>
       </c>
       <c r="D51" s="1"/>
     </row>
     <row r="52" ht="18" spans="1:5">
       <c r="B52" s="1" t="s">
-        <v>359</v>
+        <v>368</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>360</v>
+        <v>369</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>361</v>
+        <v>370</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>362</v>
+        <v>371</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -4277,34 +4390,34 @@
     </row>
     <row r="54" ht="18" spans="1:5">
       <c r="A54" t="s">
-        <v>363</v>
+        <v>372</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>364</v>
+        <v>373</v>
       </c>
     </row>
     <row r="55" ht="18" spans="1:5">
       <c r="A55" t="s">
-        <v>365</v>
+        <v>374</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>366</v>
+        <v>375</v>
       </c>
     </row>
     <row r="57" ht="18" spans="1:5">
       <c r="A57" t="s">
-        <v>367</v>
+        <v>376</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>368</v>
+        <v>377</v>
       </c>
     </row>
     <row r="59" ht="18" spans="1:5">
       <c r="A59" t="s">
-        <v>369</v>
+        <v>378</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>370</v>
+        <v>379</v>
       </c>
     </row>
   </sheetData>

--- a/副词.xlsx
+++ b/副词.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9180"/>
+    <workbookView windowWidth="22320" windowHeight="9144"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="380">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="383">
   <si>
     <t>非常，一点也不</t>
   </si>
@@ -847,6 +847,35 @@
     <t>軽々と</t>
   </si>
   <si>
+    <r>
+      <t>一步一步地，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="128"/>
+      </rPr>
+      <t>顺</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <charset val="128"/>
+      </rPr>
+      <t>利地</t>
+    </r>
+  </si>
+  <si>
+    <t>ちゃくちゃく</t>
+  </si>
+  <si>
+    <t>着々</t>
+  </si>
+  <si>
     <t>一直</t>
   </si>
   <si>
@@ -948,6 +977,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <charset val="128"/>
+      </rPr>
       <t>せめてこれだけはもらいたい｜至少也</t>
     </r>
     <r>
@@ -2735,7 +2770,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F147"/>
+  <dimension ref="A1:F148"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="16.1111111111111" style="1" customWidth="1"/>
@@ -3431,81 +3466,82 @@
       <c r="D82"/>
     </row>
     <row r="83" spans="1:5">
+      <c r="A83" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C83" s="7" t="s">
+        <v>160</v>
+      </c>
       <c r="D83"/>
     </row>
     <row r="84" spans="1:5">
-      <c r="A84" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="B84" s="1" t="s">
+      <c r="D84"/>
+    </row>
+    <row r="85" spans="1:5">
+      <c r="A85" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="B85" s="1" t="s">
         <v>38</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5">
-      <c r="B85" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="C85" s="1" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="86" spans="1:5">
       <c r="B86" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="87" spans="1:5">
-      <c r="A87" s="6" t="s">
-        <v>163</v>
-      </c>
       <c r="B87" s="1" t="s">
         <v>164</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="D87" s="1" t="s">
+    </row>
+    <row r="88" spans="1:5">
+      <c r="A88" s="6" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="88" spans="1:5">
       <c r="B88" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5">
+      <c r="B89" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="C88" s="1" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5">
-      <c r="A90" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="B90" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="C90" s="1" t="s">
+      <c r="C89" s="1" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="91" spans="1:5">
+      <c r="A91" s="6" t="s">
+        <v>171</v>
+      </c>
       <c r="B91" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="92" spans="1:5">
       <c r="B92" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="D92" s="1" t="s">
         <v>175</v>
       </c>
     </row>
@@ -3513,81 +3549,81 @@
       <c r="B93" s="1" t="s">
         <v>176</v>
       </c>
+      <c r="C93" s="1" t="s">
+        <v>177</v>
+      </c>
       <c r="D93" s="1" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5">
-      <c r="A95" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="B95" s="1" t="s">
+    </row>
+    <row r="94" spans="1:5">
+      <c r="B94" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="D95" s="1" t="s">
+      <c r="D94" s="1" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="96" spans="1:5">
-      <c r="A96" s="2" t="s">
+      <c r="A96" s="1" t="s">
         <v>181</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="C96" s="1" t="s">
+      <c r="D96" s="1" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="97" spans="1:3">
-      <c r="A97" s="2"/>
+      <c r="A97" s="2" t="s">
+        <v>184</v>
+      </c>
       <c r="B97" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="98" spans="1:3">
-      <c r="A98" s="2" t="s">
-        <v>185</v>
-      </c>
+      <c r="A98" s="2"/>
       <c r="B98" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="99" spans="1:3">
-      <c r="A99" s="5" t="s">
-        <v>187</v>
+      <c r="A99" s="2" t="s">
+        <v>188</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="100" spans="1:3">
-      <c r="A100" s="5"/>
+      <c r="A100" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>191</v>
+      </c>
     </row>
     <row r="101" spans="1:3">
-      <c r="A101" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="B101" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="C101" s="1" t="s">
-        <v>191</v>
-      </c>
+      <c r="A101" s="5"/>
     </row>
     <row r="102" spans="1:3">
-      <c r="A102" s="5"/>
+      <c r="A102" s="5" t="s">
+        <v>192</v>
+      </c>
       <c r="B102" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="103" spans="1:3">
-      <c r="A103" s="5" t="s">
-        <v>194</v>
-      </c>
+      <c r="A103" s="5"/>
       <c r="B103" s="1" t="s">
         <v>195</v>
       </c>
@@ -3596,105 +3632,105 @@
       </c>
     </row>
     <row r="104" spans="1:3">
-      <c r="A104" s="5"/>
+      <c r="A104" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>199</v>
+      </c>
     </row>
     <row r="105" spans="1:3">
-      <c r="A105" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="B105" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="C105" s="1" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="107" spans="1:3">
-      <c r="A107" s="6" t="s">
+      <c r="A105" s="5"/>
+    </row>
+    <row r="106" spans="1:3">
+      <c r="A106" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="B107" s="1" t="s">
+      <c r="B106" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="C107" s="1" t="s">
+      <c r="C106" s="1" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="109" spans="1:3">
-      <c r="A109" s="1" t="s">
+    <row r="108" spans="1:3">
+      <c r="A108" s="6" t="s">
         <v>203</v>
       </c>
-      <c r="B109" s="1" t="s">
+      <c r="B108" s="1" t="s">
         <v>204</v>
       </c>
+      <c r="C108" s="1" t="s">
+        <v>205</v>
+      </c>
     </row>
     <row r="110" spans="1:3">
-      <c r="A110" s="6" t="s">
-        <v>205</v>
+      <c r="A110" s="1" t="s">
+        <v>206</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="C110" s="1" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="112" spans="1:3">
-      <c r="A112" s="6" t="s">
+    <row r="111" spans="1:3">
+      <c r="A111" s="6" t="s">
         <v>208</v>
       </c>
-      <c r="B112" s="1" t="s">
+      <c r="B111" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4">
+      <c r="A113" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="B113" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="113" spans="1:4">
-      <c r="A113" s="6"/>
-      <c r="B113" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="C113" s="6" t="s">
-        <v>210</v>
-      </c>
-      <c r="D113" s="1" t="s">
-        <v>211</v>
-      </c>
-    </row>
     <row r="114" spans="1:4">
-      <c r="A114" s="6" t="s">
+      <c r="A114" s="6"/>
+      <c r="B114" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="B114" s="1" t="s">
+      <c r="C114" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="D114" s="1" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4">
+      <c r="A115" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="B115" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C114" s="1" t="s">
+      <c r="C115" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="115" spans="1:4">
-      <c r="A115" s="6"/>
-    </row>
     <row r="116" spans="1:4">
-      <c r="A116" s="6" t="s">
-        <v>213</v>
-      </c>
-      <c r="B116" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="C116" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="D116" s="1" t="s">
-        <v>216</v>
-      </c>
+      <c r="A116" s="6"/>
     </row>
     <row r="117" spans="1:4">
       <c r="A117" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="B117" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="B117" s="1" t="s">
+      <c r="C117" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="C117" s="1" t="s">
+      <c r="D117" s="1" t="s">
         <v>219</v>
       </c>
     </row>
@@ -3705,45 +3741,45 @@
       <c r="B118" s="1" t="s">
         <v>221</v>
       </c>
-    </row>
-    <row r="120" spans="1:4">
-      <c r="A120" s="6" t="s">
+      <c r="C118" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="B120" s="1" t="s">
+    </row>
+    <row r="119" spans="1:4">
+      <c r="A119" s="6" t="s">
         <v>223</v>
       </c>
-      <c r="C120" s="1" t="s">
+      <c r="B119" s="1" t="s">
         <v>224</v>
       </c>
     </row>
     <row r="121" spans="1:4">
-      <c r="A121" s="6"/>
+      <c r="A121" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="B121" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="C121" s="1" t="s">
+        <v>227</v>
+      </c>
     </row>
     <row r="122" spans="1:4">
-      <c r="A122" s="6" t="s">
-        <v>225</v>
-      </c>
-      <c r="B122" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="C122" s="1" t="s">
-        <v>227</v>
-      </c>
+      <c r="A122" s="6"/>
     </row>
     <row r="123" spans="1:4">
-      <c r="A123" s="6"/>
+      <c r="A123" s="6" t="s">
+        <v>228</v>
+      </c>
       <c r="B123" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="124" spans="1:4">
-      <c r="A124" s="6" t="s">
-        <v>230</v>
-      </c>
+      <c r="A124" s="6"/>
       <c r="B124" s="1" t="s">
         <v>231</v>
       </c>
@@ -3752,59 +3788,59 @@
       </c>
     </row>
     <row r="125" spans="1:4">
-      <c r="A125" s="6"/>
+      <c r="A125" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="B125" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="C125" s="1" t="s">
+        <v>235</v>
+      </c>
     </row>
     <row r="126" spans="1:4">
-      <c r="A126" s="6" t="s">
-        <v>233</v>
-      </c>
-      <c r="B126" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="C126" s="1" t="s">
-        <v>235</v>
-      </c>
+      <c r="A126" s="6"/>
     </row>
     <row r="127" spans="1:4">
-      <c r="A127" s="7" t="s">
+      <c r="A127" s="6" t="s">
         <v>236</v>
       </c>
-      <c r="B127" s="6" t="s">
+      <c r="B127" s="1" t="s">
         <v>237</v>
       </c>
+      <c r="C127" s="1" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="128" spans="1:4">
-      <c r="A128" s="6" t="s">
-        <v>238</v>
-      </c>
-      <c r="B128" s="1" t="s">
+      <c r="A128" s="7" t="s">
         <v>239</v>
       </c>
+      <c r="B128" s="6" t="s">
+        <v>240</v>
+      </c>
     </row>
     <row r="129" spans="1:4">
-      <c r="A129" s="1" t="s">
-        <v>240</v>
+      <c r="A129" s="6" t="s">
+        <v>241</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="130" spans="1:4">
-      <c r="A130" s="6" t="s">
-        <v>242</v>
+      <c r="A130" s="1" t="s">
+        <v>243</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="131" spans="1:4">
-      <c r="A131" s="4" t="s">
-        <v>244</v>
-      </c>
-      <c r="B131" s="4" t="s">
+      <c r="A131" s="6" t="s">
         <v>245</v>
       </c>
-      <c r="C131" s="4" t="s">
+      <c r="B131" s="1" t="s">
         <v>246</v>
       </c>
     </row>
@@ -3815,31 +3851,31 @@
       <c r="B132" s="4" t="s">
         <v>248</v>
       </c>
+      <c r="C132" s="4" t="s">
+        <v>249</v>
+      </c>
     </row>
     <row r="133" spans="1:4">
-      <c r="A133" s="6" t="s">
-        <v>249</v>
-      </c>
-      <c r="B133" s="1" t="s">
+      <c r="A133" s="4" t="s">
         <v>250</v>
       </c>
+      <c r="B133" s="4" t="s">
+        <v>251</v>
+      </c>
     </row>
     <row r="134" spans="1:4">
-      <c r="A134" s="8" t="s">
-        <v>251</v>
-      </c>
-      <c r="B134" s="4" t="s">
+      <c r="A134" s="6" t="s">
         <v>252</v>
       </c>
+      <c r="B134" s="1" t="s">
+        <v>253</v>
+      </c>
     </row>
     <row r="135" spans="1:4">
-      <c r="A135" s="6" t="s">
-        <v>253</v>
-      </c>
-      <c r="B135" s="1" t="s">
+      <c r="A135" s="8" t="s">
         <v>254</v>
       </c>
-      <c r="C135" s="6" t="s">
+      <c r="B135" s="4" t="s">
         <v>255</v>
       </c>
     </row>
@@ -3850,101 +3886,112 @@
       <c r="B136" s="1" t="s">
         <v>257</v>
       </c>
+      <c r="C136" s="6" t="s">
+        <v>258</v>
+      </c>
     </row>
     <row r="137" spans="1:4">
-      <c r="A137" s="9" t="s">
-        <v>258</v>
+      <c r="A137" s="6" t="s">
+        <v>259</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="C137" s="6" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="138" spans="1:4">
-      <c r="A138" s="6" t="s">
+      <c r="A138" s="9" t="s">
         <v>261</v>
       </c>
       <c r="B138" s="1" t="s">
         <v>262</v>
       </c>
+      <c r="C138" s="6" t="s">
+        <v>263</v>
+      </c>
     </row>
     <row r="139" spans="1:4">
-      <c r="A139" s="1" t="s">
-        <v>263</v>
+      <c r="A139" s="6" t="s">
+        <v>264</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="C139" s="1" t="s">
         <v>265</v>
-      </c>
-      <c r="D139" s="1" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="140" spans="1:4">
       <c r="A140" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="B140" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="B140" s="1" t="s">
+      <c r="C140" s="1" t="s">
         <v>268</v>
       </c>
+      <c r="D140" s="1" t="s">
+        <v>269</v>
+      </c>
     </row>
     <row r="141" spans="1:4">
-      <c r="A141" s="6" t="s">
-        <v>269</v>
+      <c r="A141" s="1" t="s">
+        <v>270</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="142" spans="1:4">
-      <c r="A142" s="6"/>
+      <c r="A142" s="6" t="s">
+        <v>272</v>
+      </c>
       <c r="B142" s="1" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="143" spans="1:4">
-      <c r="A143" s="6" t="s">
-        <v>272</v>
-      </c>
+      <c r="A143" s="6"/>
       <c r="B143" s="1" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="144" spans="1:4">
+      <c r="A144" s="6" t="s">
+        <v>275</v>
+      </c>
       <c r="B144" s="1" t="s">
-        <v>274</v>
-      </c>
-      <c r="C144" s="1" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="145" spans="1:3">
-      <c r="A145" s="6"/>
-      <c r="B145" s="4" t="s">
+      <c r="B145" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="C145" s="1" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3">
+      <c r="A146" s="6"/>
+      <c r="B146" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="C146" s="4" t="s">
         <v>276</v>
       </c>
-      <c r="C145" s="4" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="146" spans="1:3">
-      <c r="A146" s="7" t="s">
-        <v>277</v>
-      </c>
-      <c r="B146" s="6" t="s">
-        <v>278</v>
-      </c>
     </row>
     <row r="147" spans="1:3">
-      <c r="A147" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="B147" s="1" t="s">
+      <c r="A147" s="7" t="s">
         <v>280</v>
+      </c>
+      <c r="B147" s="6" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3">
+      <c r="A148" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="B148" s="1" t="s">
+        <v>283</v>
       </c>
     </row>
   </sheetData>
@@ -3966,67 +4013,67 @@
   <sheetData>
     <row r="1" ht="18" spans="1:3">
       <c r="A1" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="2" ht="18" spans="1:3">
       <c r="B2" s="1" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:3">
       <c r="B3" s="1" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:3">
       <c r="B4" s="1" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:3">
       <c r="B5" s="1" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:3">
       <c r="B6" s="1" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:3">
       <c r="A7" s="1" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:3">
       <c r="A8" s="1"/>
       <c r="B8" s="1" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="C8" s="1"/>
     </row>
@@ -4037,83 +4084,83 @@
     </row>
     <row r="10" ht="18" spans="1:3">
       <c r="A10" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
     </row>
     <row r="11" ht="18" spans="1:3">
       <c r="B11" s="1" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="13" ht="18" spans="1:3">
       <c r="A13" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="14" ht="18" spans="1:3">
       <c r="B14" s="1" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="C14" s="1"/>
     </row>
     <row r="15" ht="18" spans="1:3">
       <c r="B15" s="1" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="C15" s="1"/>
     </row>
     <row r="16" ht="18" spans="1:3">
       <c r="B16" s="1" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
     </row>
     <row r="17" ht="18" spans="1:4">
       <c r="B17" s="1" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="C17" s="1"/>
     </row>
     <row r="18" ht="18" spans="1:4">
       <c r="B18" s="1" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="C18" s="1"/>
     </row>
     <row r="19" ht="18" spans="1:4">
       <c r="B19" s="1" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="C19" s="1"/>
     </row>
     <row r="20" ht="18" spans="1:4">
       <c r="B20" s="1" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="21" ht="18" spans="1:4">
       <c r="B21" s="1" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="22" ht="18" spans="1:4">
@@ -4122,57 +4169,57 @@
     </row>
     <row r="23" ht="18" spans="1:4">
       <c r="A23" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="C23" s="1"/>
     </row>
     <row r="24" ht="18" spans="1:4">
       <c r="B24" s="1" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="C24" s="1"/>
     </row>
     <row r="25" ht="18" spans="1:4">
       <c r="B25" s="1" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="26" ht="18" spans="1:4">
       <c r="A26" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="D26" s="3"/>
     </row>
     <row r="27" ht="18" spans="1:4">
       <c r="A27" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="C27" s="1"/>
     </row>
     <row r="28" ht="18" spans="1:4">
       <c r="B28" s="1" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
     </row>
     <row r="29" ht="18" spans="1:4">
@@ -4181,68 +4228,68 @@
     </row>
     <row r="30" ht="18" spans="1:4">
       <c r="A30" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="C30" s="1"/>
     </row>
     <row r="31" ht="18" spans="1:4">
       <c r="B31" s="1" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="C31" s="1"/>
     </row>
     <row r="32" ht="18" spans="1:4">
       <c r="B32" s="1" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="C32" s="1"/>
     </row>
     <row r="33" ht="18" spans="1:4">
       <c r="B33" s="4" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="C33" s="1"/>
     </row>
     <row r="34" ht="18" spans="1:4">
       <c r="B34" s="4" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="C34" s="1"/>
     </row>
     <row r="35" ht="18" spans="1:4">
       <c r="B35" s="4" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="36" ht="18" spans="1:4">
       <c r="B36" s="4" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="37" ht="18" spans="1:4">
       <c r="B37" s="4" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
     </row>
     <row r="38" ht="18" spans="1:4">
@@ -4252,38 +4299,38 @@
     </row>
     <row r="39" ht="18" spans="1:4">
       <c r="A39" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="C39" s="1"/>
       <c r="D39" s="1"/>
     </row>
     <row r="40" ht="18" spans="1:4">
       <c r="B40" s="4" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="D40" s="1"/>
     </row>
     <row r="41" ht="18" spans="1:4">
       <c r="B41" s="4" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="D41" s="1"/>
     </row>
     <row r="42" ht="18" spans="1:4">
       <c r="B42" s="4" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="D42" s="1"/>
     </row>
@@ -4294,41 +4341,41 @@
     </row>
     <row r="44" ht="18" spans="1:4">
       <c r="A44" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="D44" s="1"/>
     </row>
     <row r="45" ht="18" spans="1:4">
       <c r="B45" s="1" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="D45" s="1"/>
     </row>
     <row r="46" ht="18" spans="1:4">
       <c r="B46" s="1" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="C46" s="4"/>
       <c r="D46" s="1"/>
     </row>
     <row r="47" ht="18" spans="1:4">
       <c r="A47" s="3" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="D47" s="1"/>
     </row>
@@ -4338,51 +4385,51 @@
     </row>
     <row r="49" ht="18" spans="1:5">
       <c r="A49" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="D49" s="5"/>
     </row>
     <row r="50" ht="18" spans="1:5">
       <c r="A50" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
     </row>
     <row r="51" ht="18" spans="1:5">
       <c r="B51" s="1" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="D51" s="1"/>
     </row>
     <row r="52" ht="18" spans="1:5">
       <c r="B52" s="1" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -4390,34 +4437,34 @@
     </row>
     <row r="54" ht="18" spans="1:5">
       <c r="A54" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
     </row>
     <row r="55" ht="18" spans="1:5">
       <c r="A55" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="57" ht="18" spans="1:5">
       <c r="A57" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
     </row>
     <row r="59" ht="18" spans="1:5">
       <c r="A59" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
     </row>
   </sheetData>
